--- a/public/sample_uploads/investor_kpi_mappings_update.xlsx
+++ b/public/sample_uploads/investor_kpi_mappings_update.xlsx
@@ -19,8 +19,48 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Optional
+Input Yes if the values should to be aggregated, No otherwise.
+For example - Monthly revenue numbers can be tagged yes to cumulate to qrt ytd. Employee count should be tagged as no</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Optional, input when Auto Fill is selected as Compute
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t xml:space="preserve">Stakeholder</t>
   </si>
@@ -52,7 +92,10 @@
     <t xml:space="preserve">Upper Threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Cumulate</t>
+    <t xml:space="preserve">Auto fill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compute Formula</t>
   </si>
   <si>
     <t xml:space="preserve">Update Only</t>
@@ -74,6 +117,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -98,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -126,6 +172,26 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -135,12 +201,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -173,7 +246,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,6 +256,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -314,7 +395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M1003"/>
   <sheetFormatPr defaultColWidth="9.47265625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.93"/>
@@ -326,7 +407,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="21.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -363,32 +445,35 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
@@ -396,34 +481,34 @@
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>18</v>
+      <c r="K2" s="5" t="s">
+        <v>19</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>18</v>
+      <c r="M2" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
@@ -431,14 +516,3020 @@
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>18</v>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>18</v>
+      <c r="M3" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K40" s="5"/>
+    </row>
+    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" s="5"/>
+    </row>
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K44" s="5"/>
+    </row>
+    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K53" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" s="5"/>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K56" s="5"/>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K57" s="5"/>
+    </row>
+    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K59" s="5"/>
+    </row>
+    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K60" s="5"/>
+    </row>
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K62" s="5"/>
+    </row>
+    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K63" s="5"/>
+    </row>
+    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K64" s="5"/>
+    </row>
+    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" s="5"/>
+    </row>
+    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K67" s="5"/>
+    </row>
+    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K68" s="5"/>
+    </row>
+    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K69" s="5"/>
+    </row>
+    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K71" s="5"/>
+    </row>
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K72" s="5"/>
+    </row>
+    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K73" s="5"/>
+    </row>
+    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K75" s="5"/>
+    </row>
+    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K76" s="5"/>
+    </row>
+    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K77" s="5"/>
+    </row>
+    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K78" s="5"/>
+    </row>
+    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K79" s="5"/>
+    </row>
+    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K82" s="5"/>
+    </row>
+    <row r="83" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K83" s="5"/>
+    </row>
+    <row r="84" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K84" s="5"/>
+    </row>
+    <row r="85" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K90" s="5"/>
+    </row>
+    <row r="91" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K91" s="5"/>
+    </row>
+    <row r="92" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K92" s="5"/>
+    </row>
+    <row r="93" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K93" s="5"/>
+    </row>
+    <row r="94" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K95" s="5"/>
+    </row>
+    <row r="96" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K96" s="5"/>
+    </row>
+    <row r="97" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K97" s="5"/>
+    </row>
+    <row r="98" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K98" s="5"/>
+    </row>
+    <row r="99" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K99" s="5"/>
+    </row>
+    <row r="100" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K100" s="5"/>
+    </row>
+    <row r="101" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K101" s="5"/>
+    </row>
+    <row r="102" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K102" s="5"/>
+    </row>
+    <row r="103" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K103" s="5"/>
+    </row>
+    <row r="104" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K104" s="5"/>
+    </row>
+    <row r="105" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K105" s="5"/>
+    </row>
+    <row r="106" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K106" s="5"/>
+    </row>
+    <row r="107" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K107" s="5"/>
+    </row>
+    <row r="108" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K108" s="5"/>
+    </row>
+    <row r="109" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K109" s="5"/>
+    </row>
+    <row r="110" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K110" s="5"/>
+    </row>
+    <row r="111" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K111" s="5"/>
+    </row>
+    <row r="112" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K112" s="5"/>
+    </row>
+    <row r="113" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K113" s="5"/>
+    </row>
+    <row r="114" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K114" s="5"/>
+    </row>
+    <row r="115" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K115" s="5"/>
+    </row>
+    <row r="116" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K116" s="5"/>
+    </row>
+    <row r="117" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K117" s="5"/>
+    </row>
+    <row r="118" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K118" s="5"/>
+    </row>
+    <row r="119" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K119" s="5"/>
+    </row>
+    <row r="120" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K120" s="5"/>
+    </row>
+    <row r="121" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K121" s="5"/>
+    </row>
+    <row r="122" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K122" s="5"/>
+    </row>
+    <row r="123" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K123" s="5"/>
+    </row>
+    <row r="124" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K124" s="5"/>
+    </row>
+    <row r="125" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K125" s="5"/>
+    </row>
+    <row r="126" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K126" s="5"/>
+    </row>
+    <row r="127" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K127" s="5"/>
+    </row>
+    <row r="128" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K128" s="5"/>
+    </row>
+    <row r="129" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K129" s="5"/>
+    </row>
+    <row r="130" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K130" s="5"/>
+    </row>
+    <row r="131" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K131" s="5"/>
+    </row>
+    <row r="132" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K132" s="5"/>
+    </row>
+    <row r="133" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K133" s="5"/>
+    </row>
+    <row r="134" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K134" s="5"/>
+    </row>
+    <row r="135" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K135" s="5"/>
+    </row>
+    <row r="136" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K136" s="5"/>
+    </row>
+    <row r="137" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K137" s="5"/>
+    </row>
+    <row r="138" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K138" s="5"/>
+    </row>
+    <row r="139" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K139" s="5"/>
+    </row>
+    <row r="140" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K140" s="5"/>
+    </row>
+    <row r="141" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K141" s="5"/>
+    </row>
+    <row r="142" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K142" s="5"/>
+    </row>
+    <row r="143" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K143" s="5"/>
+    </row>
+    <row r="144" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K144" s="5"/>
+    </row>
+    <row r="145" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K145" s="5"/>
+    </row>
+    <row r="146" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K146" s="5"/>
+    </row>
+    <row r="147" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K147" s="5"/>
+    </row>
+    <row r="148" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K148" s="5"/>
+    </row>
+    <row r="149" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K149" s="5"/>
+    </row>
+    <row r="150" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K150" s="5"/>
+    </row>
+    <row r="151" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K151" s="5"/>
+    </row>
+    <row r="152" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K152" s="5"/>
+    </row>
+    <row r="153" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K153" s="5"/>
+    </row>
+    <row r="154" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K154" s="5"/>
+    </row>
+    <row r="155" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K155" s="5"/>
+    </row>
+    <row r="156" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K156" s="5"/>
+    </row>
+    <row r="157" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K157" s="5"/>
+    </row>
+    <row r="158" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K158" s="5"/>
+    </row>
+    <row r="159" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K159" s="5"/>
+    </row>
+    <row r="160" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K160" s="5"/>
+    </row>
+    <row r="161" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K161" s="5"/>
+    </row>
+    <row r="162" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K162" s="5"/>
+    </row>
+    <row r="163" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K163" s="5"/>
+    </row>
+    <row r="164" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K164" s="5"/>
+    </row>
+    <row r="165" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K165" s="5"/>
+    </row>
+    <row r="166" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K166" s="5"/>
+    </row>
+    <row r="167" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K167" s="5"/>
+    </row>
+    <row r="168" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K168" s="5"/>
+    </row>
+    <row r="169" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K169" s="5"/>
+    </row>
+    <row r="170" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K170" s="5"/>
+    </row>
+    <row r="171" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K171" s="5"/>
+    </row>
+    <row r="172" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K172" s="5"/>
+    </row>
+    <row r="173" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K173" s="5"/>
+    </row>
+    <row r="174" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K174" s="5"/>
+    </row>
+    <row r="175" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K175" s="5"/>
+    </row>
+    <row r="176" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K176" s="5"/>
+    </row>
+    <row r="177" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K177" s="5"/>
+    </row>
+    <row r="178" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K178" s="5"/>
+    </row>
+    <row r="179" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K179" s="5"/>
+    </row>
+    <row r="180" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K180" s="5"/>
+    </row>
+    <row r="181" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K181" s="5"/>
+    </row>
+    <row r="182" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K182" s="5"/>
+    </row>
+    <row r="183" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K183" s="5"/>
+    </row>
+    <row r="184" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K184" s="5"/>
+    </row>
+    <row r="185" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K185" s="5"/>
+    </row>
+    <row r="186" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K186" s="5"/>
+    </row>
+    <row r="187" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K187" s="5"/>
+    </row>
+    <row r="188" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K188" s="5"/>
+    </row>
+    <row r="189" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K189" s="5"/>
+    </row>
+    <row r="190" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K190" s="5"/>
+    </row>
+    <row r="191" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K191" s="5"/>
+    </row>
+    <row r="192" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K192" s="5"/>
+    </row>
+    <row r="193" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K193" s="5"/>
+    </row>
+    <row r="194" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K194" s="5"/>
+    </row>
+    <row r="195" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K195" s="5"/>
+    </row>
+    <row r="196" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K196" s="5"/>
+    </row>
+    <row r="197" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K197" s="5"/>
+    </row>
+    <row r="198" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K198" s="5"/>
+    </row>
+    <row r="199" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K199" s="5"/>
+    </row>
+    <row r="200" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K200" s="5"/>
+    </row>
+    <row r="201" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K201" s="5"/>
+    </row>
+    <row r="202" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K202" s="5"/>
+    </row>
+    <row r="203" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K203" s="5"/>
+    </row>
+    <row r="204" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K204" s="5"/>
+    </row>
+    <row r="205" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K205" s="5"/>
+    </row>
+    <row r="206" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K206" s="5"/>
+    </row>
+    <row r="207" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K207" s="5"/>
+    </row>
+    <row r="208" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K208" s="5"/>
+    </row>
+    <row r="209" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K209" s="5"/>
+    </row>
+    <row r="210" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K210" s="5"/>
+    </row>
+    <row r="211" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K211" s="5"/>
+    </row>
+    <row r="212" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K212" s="5"/>
+    </row>
+    <row r="213" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K213" s="5"/>
+    </row>
+    <row r="214" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K214" s="5"/>
+    </row>
+    <row r="215" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K215" s="5"/>
+    </row>
+    <row r="216" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K216" s="5"/>
+    </row>
+    <row r="217" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K217" s="5"/>
+    </row>
+    <row r="218" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K218" s="5"/>
+    </row>
+    <row r="219" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K219" s="5"/>
+    </row>
+    <row r="220" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K220" s="5"/>
+    </row>
+    <row r="221" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K221" s="5"/>
+    </row>
+    <row r="222" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K222" s="5"/>
+    </row>
+    <row r="223" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K223" s="5"/>
+    </row>
+    <row r="224" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K224" s="5"/>
+    </row>
+    <row r="225" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K225" s="5"/>
+    </row>
+    <row r="226" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K226" s="5"/>
+    </row>
+    <row r="227" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K227" s="5"/>
+    </row>
+    <row r="228" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K228" s="5"/>
+    </row>
+    <row r="229" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K229" s="5"/>
+    </row>
+    <row r="230" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K230" s="5"/>
+    </row>
+    <row r="231" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K231" s="5"/>
+    </row>
+    <row r="232" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K232" s="5"/>
+    </row>
+    <row r="233" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K233" s="5"/>
+    </row>
+    <row r="234" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K234" s="5"/>
+    </row>
+    <row r="235" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K235" s="5"/>
+    </row>
+    <row r="236" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K236" s="5"/>
+    </row>
+    <row r="237" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K237" s="5"/>
+    </row>
+    <row r="238" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K238" s="5"/>
+    </row>
+    <row r="239" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K239" s="5"/>
+    </row>
+    <row r="240" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K240" s="5"/>
+    </row>
+    <row r="241" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K241" s="5"/>
+    </row>
+    <row r="242" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K242" s="5"/>
+    </row>
+    <row r="243" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K243" s="5"/>
+    </row>
+    <row r="244" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K244" s="5"/>
+    </row>
+    <row r="245" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K245" s="5"/>
+    </row>
+    <row r="246" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K246" s="5"/>
+    </row>
+    <row r="247" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K247" s="5"/>
+    </row>
+    <row r="248" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K248" s="5"/>
+    </row>
+    <row r="249" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K249" s="5"/>
+    </row>
+    <row r="250" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K250" s="5"/>
+    </row>
+    <row r="251" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K251" s="5"/>
+    </row>
+    <row r="252" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K252" s="5"/>
+    </row>
+    <row r="253" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K253" s="5"/>
+    </row>
+    <row r="254" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K254" s="5"/>
+    </row>
+    <row r="255" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K255" s="5"/>
+    </row>
+    <row r="256" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K256" s="5"/>
+    </row>
+    <row r="257" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K257" s="5"/>
+    </row>
+    <row r="258" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K258" s="5"/>
+    </row>
+    <row r="259" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K259" s="5"/>
+    </row>
+    <row r="260" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K260" s="5"/>
+    </row>
+    <row r="261" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K261" s="5"/>
+    </row>
+    <row r="262" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K262" s="5"/>
+    </row>
+    <row r="263" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K263" s="5"/>
+    </row>
+    <row r="264" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K264" s="5"/>
+    </row>
+    <row r="265" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K265" s="5"/>
+    </row>
+    <row r="266" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K266" s="5"/>
+    </row>
+    <row r="267" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K267" s="5"/>
+    </row>
+    <row r="268" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K268" s="5"/>
+    </row>
+    <row r="269" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K269" s="5"/>
+    </row>
+    <row r="270" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K270" s="5"/>
+    </row>
+    <row r="271" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K271" s="5"/>
+    </row>
+    <row r="272" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K272" s="5"/>
+    </row>
+    <row r="273" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K273" s="5"/>
+    </row>
+    <row r="274" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K274" s="5"/>
+    </row>
+    <row r="275" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K275" s="5"/>
+    </row>
+    <row r="276" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K276" s="5"/>
+    </row>
+    <row r="277" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K277" s="5"/>
+    </row>
+    <row r="278" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K278" s="5"/>
+    </row>
+    <row r="279" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K279" s="5"/>
+    </row>
+    <row r="280" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K280" s="5"/>
+    </row>
+    <row r="281" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K281" s="5"/>
+    </row>
+    <row r="282" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K282" s="5"/>
+    </row>
+    <row r="283" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K283" s="5"/>
+    </row>
+    <row r="284" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K284" s="5"/>
+    </row>
+    <row r="285" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K285" s="5"/>
+    </row>
+    <row r="286" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K286" s="5"/>
+    </row>
+    <row r="287" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K287" s="5"/>
+    </row>
+    <row r="288" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K288" s="5"/>
+    </row>
+    <row r="289" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K289" s="5"/>
+    </row>
+    <row r="290" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K290" s="5"/>
+    </row>
+    <row r="291" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K291" s="5"/>
+    </row>
+    <row r="292" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K292" s="5"/>
+    </row>
+    <row r="293" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K293" s="5"/>
+    </row>
+    <row r="294" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K294" s="5"/>
+    </row>
+    <row r="295" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K295" s="5"/>
+    </row>
+    <row r="296" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K296" s="5"/>
+    </row>
+    <row r="297" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K297" s="5"/>
+    </row>
+    <row r="298" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K298" s="5"/>
+    </row>
+    <row r="299" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K299" s="5"/>
+    </row>
+    <row r="300" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K300" s="5"/>
+    </row>
+    <row r="301" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K301" s="5"/>
+    </row>
+    <row r="302" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K302" s="5"/>
+    </row>
+    <row r="303" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K303" s="5"/>
+    </row>
+    <row r="304" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K304" s="5"/>
+    </row>
+    <row r="305" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K305" s="5"/>
+    </row>
+    <row r="306" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K306" s="5"/>
+    </row>
+    <row r="307" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K307" s="5"/>
+    </row>
+    <row r="308" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K308" s="5"/>
+    </row>
+    <row r="309" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K309" s="5"/>
+    </row>
+    <row r="310" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K310" s="5"/>
+    </row>
+    <row r="311" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K311" s="5"/>
+    </row>
+    <row r="312" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K312" s="5"/>
+    </row>
+    <row r="313" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K313" s="5"/>
+    </row>
+    <row r="314" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K314" s="5"/>
+    </row>
+    <row r="315" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K315" s="5"/>
+    </row>
+    <row r="316" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K316" s="5"/>
+    </row>
+    <row r="317" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K317" s="5"/>
+    </row>
+    <row r="318" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K318" s="5"/>
+    </row>
+    <row r="319" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K319" s="5"/>
+    </row>
+    <row r="320" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K320" s="5"/>
+    </row>
+    <row r="321" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K321" s="5"/>
+    </row>
+    <row r="322" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K322" s="5"/>
+    </row>
+    <row r="323" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K323" s="5"/>
+    </row>
+    <row r="324" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K324" s="5"/>
+    </row>
+    <row r="325" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K325" s="5"/>
+    </row>
+    <row r="326" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K326" s="5"/>
+    </row>
+    <row r="327" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K327" s="5"/>
+    </row>
+    <row r="328" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K328" s="5"/>
+    </row>
+    <row r="329" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K329" s="5"/>
+    </row>
+    <row r="330" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K330" s="5"/>
+    </row>
+    <row r="331" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K331" s="5"/>
+    </row>
+    <row r="332" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K332" s="5"/>
+    </row>
+    <row r="333" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K333" s="5"/>
+    </row>
+    <row r="334" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K334" s="5"/>
+    </row>
+    <row r="335" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K335" s="5"/>
+    </row>
+    <row r="336" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K336" s="5"/>
+    </row>
+    <row r="337" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K337" s="5"/>
+    </row>
+    <row r="338" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K338" s="5"/>
+    </row>
+    <row r="339" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K339" s="5"/>
+    </row>
+    <row r="340" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K340" s="5"/>
+    </row>
+    <row r="341" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K341" s="5"/>
+    </row>
+    <row r="342" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K342" s="5"/>
+    </row>
+    <row r="343" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K343" s="5"/>
+    </row>
+    <row r="344" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K344" s="5"/>
+    </row>
+    <row r="345" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K345" s="5"/>
+    </row>
+    <row r="346" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K346" s="5"/>
+    </row>
+    <row r="347" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K347" s="5"/>
+    </row>
+    <row r="348" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K348" s="5"/>
+    </row>
+    <row r="349" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K349" s="5"/>
+    </row>
+    <row r="350" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K350" s="5"/>
+    </row>
+    <row r="351" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K351" s="5"/>
+    </row>
+    <row r="352" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K352" s="5"/>
+    </row>
+    <row r="353" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K353" s="5"/>
+    </row>
+    <row r="354" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K354" s="5"/>
+    </row>
+    <row r="355" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K355" s="5"/>
+    </row>
+    <row r="356" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K356" s="5"/>
+    </row>
+    <row r="357" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K357" s="5"/>
+    </row>
+    <row r="358" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K358" s="5"/>
+    </row>
+    <row r="359" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K359" s="5"/>
+    </row>
+    <row r="360" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K360" s="5"/>
+    </row>
+    <row r="361" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K361" s="5"/>
+    </row>
+    <row r="362" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K362" s="5"/>
+    </row>
+    <row r="363" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K363" s="5"/>
+    </row>
+    <row r="364" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K364" s="5"/>
+    </row>
+    <row r="365" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K365" s="5"/>
+    </row>
+    <row r="366" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K366" s="5"/>
+    </row>
+    <row r="367" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K367" s="5"/>
+    </row>
+    <row r="368" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K368" s="5"/>
+    </row>
+    <row r="369" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K369" s="5"/>
+    </row>
+    <row r="370" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K370" s="5"/>
+    </row>
+    <row r="371" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K371" s="5"/>
+    </row>
+    <row r="372" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K372" s="5"/>
+    </row>
+    <row r="373" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K373" s="5"/>
+    </row>
+    <row r="374" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K374" s="5"/>
+    </row>
+    <row r="375" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K375" s="5"/>
+    </row>
+    <row r="376" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K376" s="5"/>
+    </row>
+    <row r="377" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K377" s="5"/>
+    </row>
+    <row r="378" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K378" s="5"/>
+    </row>
+    <row r="379" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K379" s="5"/>
+    </row>
+    <row r="380" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K380" s="5"/>
+    </row>
+    <row r="381" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K381" s="5"/>
+    </row>
+    <row r="382" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K382" s="5"/>
+    </row>
+    <row r="383" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K383" s="5"/>
+    </row>
+    <row r="384" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K384" s="5"/>
+    </row>
+    <row r="385" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K385" s="5"/>
+    </row>
+    <row r="386" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K386" s="5"/>
+    </row>
+    <row r="387" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K387" s="5"/>
+    </row>
+    <row r="388" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K388" s="5"/>
+    </row>
+    <row r="389" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K389" s="5"/>
+    </row>
+    <row r="390" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K390" s="5"/>
+    </row>
+    <row r="391" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K391" s="5"/>
+    </row>
+    <row r="392" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K392" s="5"/>
+    </row>
+    <row r="393" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K393" s="5"/>
+    </row>
+    <row r="394" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K394" s="5"/>
+    </row>
+    <row r="395" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K395" s="5"/>
+    </row>
+    <row r="396" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K396" s="5"/>
+    </row>
+    <row r="397" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K397" s="5"/>
+    </row>
+    <row r="398" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K398" s="5"/>
+    </row>
+    <row r="399" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K399" s="5"/>
+    </row>
+    <row r="400" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K400" s="5"/>
+    </row>
+    <row r="401" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K401" s="5"/>
+    </row>
+    <row r="402" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K402" s="5"/>
+    </row>
+    <row r="403" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K403" s="5"/>
+    </row>
+    <row r="404" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K404" s="5"/>
+    </row>
+    <row r="405" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K405" s="5"/>
+    </row>
+    <row r="406" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K406" s="5"/>
+    </row>
+    <row r="407" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K407" s="5"/>
+    </row>
+    <row r="408" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K408" s="5"/>
+    </row>
+    <row r="409" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K409" s="5"/>
+    </row>
+    <row r="410" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K410" s="5"/>
+    </row>
+    <row r="411" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K411" s="5"/>
+    </row>
+    <row r="412" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K412" s="5"/>
+    </row>
+    <row r="413" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K413" s="5"/>
+    </row>
+    <row r="414" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K414" s="5"/>
+    </row>
+    <row r="415" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K415" s="5"/>
+    </row>
+    <row r="416" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K416" s="5"/>
+    </row>
+    <row r="417" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K417" s="5"/>
+    </row>
+    <row r="418" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K418" s="5"/>
+    </row>
+    <row r="419" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K419" s="5"/>
+    </row>
+    <row r="420" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K420" s="5"/>
+    </row>
+    <row r="421" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K421" s="5"/>
+    </row>
+    <row r="422" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K422" s="5"/>
+    </row>
+    <row r="423" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K423" s="5"/>
+    </row>
+    <row r="424" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K424" s="5"/>
+    </row>
+    <row r="425" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K425" s="5"/>
+    </row>
+    <row r="426" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K426" s="5"/>
+    </row>
+    <row r="427" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K427" s="5"/>
+    </row>
+    <row r="428" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K428" s="5"/>
+    </row>
+    <row r="429" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K429" s="5"/>
+    </row>
+    <row r="430" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K430" s="5"/>
+    </row>
+    <row r="431" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K431" s="5"/>
+    </row>
+    <row r="432" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K432" s="5"/>
+    </row>
+    <row r="433" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K433" s="5"/>
+    </row>
+    <row r="434" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K434" s="5"/>
+    </row>
+    <row r="435" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K435" s="5"/>
+    </row>
+    <row r="436" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K436" s="5"/>
+    </row>
+    <row r="437" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K437" s="5"/>
+    </row>
+    <row r="438" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K438" s="5"/>
+    </row>
+    <row r="439" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K439" s="5"/>
+    </row>
+    <row r="440" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K440" s="5"/>
+    </row>
+    <row r="441" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K441" s="5"/>
+    </row>
+    <row r="442" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K442" s="5"/>
+    </row>
+    <row r="443" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K443" s="5"/>
+    </row>
+    <row r="444" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K444" s="5"/>
+    </row>
+    <row r="445" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K445" s="5"/>
+    </row>
+    <row r="446" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K446" s="5"/>
+    </row>
+    <row r="447" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K447" s="5"/>
+    </row>
+    <row r="448" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K448" s="5"/>
+    </row>
+    <row r="449" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K449" s="5"/>
+    </row>
+    <row r="450" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K450" s="5"/>
+    </row>
+    <row r="451" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K451" s="5"/>
+    </row>
+    <row r="452" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K452" s="5"/>
+    </row>
+    <row r="453" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K453" s="5"/>
+    </row>
+    <row r="454" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K454" s="5"/>
+    </row>
+    <row r="455" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K455" s="5"/>
+    </row>
+    <row r="456" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K456" s="5"/>
+    </row>
+    <row r="457" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K457" s="5"/>
+    </row>
+    <row r="458" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K458" s="5"/>
+    </row>
+    <row r="459" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K459" s="5"/>
+    </row>
+    <row r="460" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K460" s="5"/>
+    </row>
+    <row r="461" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K461" s="5"/>
+    </row>
+    <row r="462" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K462" s="5"/>
+    </row>
+    <row r="463" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K463" s="5"/>
+    </row>
+    <row r="464" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K464" s="5"/>
+    </row>
+    <row r="465" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K465" s="5"/>
+    </row>
+    <row r="466" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K466" s="5"/>
+    </row>
+    <row r="467" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K467" s="5"/>
+    </row>
+    <row r="468" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K468" s="5"/>
+    </row>
+    <row r="469" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K469" s="5"/>
+    </row>
+    <row r="470" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K470" s="5"/>
+    </row>
+    <row r="471" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K471" s="5"/>
+    </row>
+    <row r="472" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K472" s="5"/>
+    </row>
+    <row r="473" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K473" s="5"/>
+    </row>
+    <row r="474" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K474" s="5"/>
+    </row>
+    <row r="475" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K475" s="5"/>
+    </row>
+    <row r="476" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K476" s="5"/>
+    </row>
+    <row r="477" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K477" s="5"/>
+    </row>
+    <row r="478" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K478" s="5"/>
+    </row>
+    <row r="479" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K479" s="5"/>
+    </row>
+    <row r="480" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K480" s="5"/>
+    </row>
+    <row r="481" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K481" s="5"/>
+    </row>
+    <row r="482" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K482" s="5"/>
+    </row>
+    <row r="483" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K483" s="5"/>
+    </row>
+    <row r="484" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K484" s="5"/>
+    </row>
+    <row r="485" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K485" s="5"/>
+    </row>
+    <row r="486" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K486" s="5"/>
+    </row>
+    <row r="487" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K487" s="5"/>
+    </row>
+    <row r="488" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K488" s="5"/>
+    </row>
+    <row r="489" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K489" s="5"/>
+    </row>
+    <row r="490" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K490" s="5"/>
+    </row>
+    <row r="491" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K491" s="5"/>
+    </row>
+    <row r="492" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K492" s="5"/>
+    </row>
+    <row r="493" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K493" s="5"/>
+    </row>
+    <row r="494" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K494" s="5"/>
+    </row>
+    <row r="495" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K495" s="5"/>
+    </row>
+    <row r="496" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K496" s="5"/>
+    </row>
+    <row r="497" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K497" s="5"/>
+    </row>
+    <row r="498" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K498" s="5"/>
+    </row>
+    <row r="499" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K499" s="5"/>
+    </row>
+    <row r="500" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K500" s="5"/>
+    </row>
+    <row r="501" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K501" s="5"/>
+    </row>
+    <row r="502" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K502" s="5"/>
+    </row>
+    <row r="503" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K503" s="5"/>
+    </row>
+    <row r="504" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K504" s="5"/>
+    </row>
+    <row r="505" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K505" s="5"/>
+    </row>
+    <row r="506" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K506" s="5"/>
+    </row>
+    <row r="507" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K507" s="5"/>
+    </row>
+    <row r="508" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K508" s="5"/>
+    </row>
+    <row r="509" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K509" s="5"/>
+    </row>
+    <row r="510" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K510" s="5"/>
+    </row>
+    <row r="511" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K511" s="5"/>
+    </row>
+    <row r="512" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K512" s="5"/>
+    </row>
+    <row r="513" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K513" s="5"/>
+    </row>
+    <row r="514" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K514" s="5"/>
+    </row>
+    <row r="515" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K515" s="5"/>
+    </row>
+    <row r="516" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K516" s="5"/>
+    </row>
+    <row r="517" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K517" s="5"/>
+    </row>
+    <row r="518" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K518" s="5"/>
+    </row>
+    <row r="519" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K519" s="5"/>
+    </row>
+    <row r="520" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K520" s="5"/>
+    </row>
+    <row r="521" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K521" s="5"/>
+    </row>
+    <row r="522" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K522" s="5"/>
+    </row>
+    <row r="523" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K523" s="5"/>
+    </row>
+    <row r="524" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K524" s="5"/>
+    </row>
+    <row r="525" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K525" s="5"/>
+    </row>
+    <row r="526" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K526" s="5"/>
+    </row>
+    <row r="527" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K527" s="5"/>
+    </row>
+    <row r="528" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K528" s="5"/>
+    </row>
+    <row r="529" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K529" s="5"/>
+    </row>
+    <row r="530" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K530" s="5"/>
+    </row>
+    <row r="531" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K531" s="5"/>
+    </row>
+    <row r="532" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K532" s="5"/>
+    </row>
+    <row r="533" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K533" s="5"/>
+    </row>
+    <row r="534" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K534" s="5"/>
+    </row>
+    <row r="535" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K535" s="5"/>
+    </row>
+    <row r="536" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K536" s="5"/>
+    </row>
+    <row r="537" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K537" s="5"/>
+    </row>
+    <row r="538" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K538" s="5"/>
+    </row>
+    <row r="539" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K539" s="5"/>
+    </row>
+    <row r="540" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K540" s="5"/>
+    </row>
+    <row r="541" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K541" s="5"/>
+    </row>
+    <row r="542" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K542" s="5"/>
+    </row>
+    <row r="543" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K543" s="5"/>
+    </row>
+    <row r="544" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K544" s="5"/>
+    </row>
+    <row r="545" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K545" s="5"/>
+    </row>
+    <row r="546" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K546" s="5"/>
+    </row>
+    <row r="547" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K547" s="5"/>
+    </row>
+    <row r="548" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K548" s="5"/>
+    </row>
+    <row r="549" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K549" s="5"/>
+    </row>
+    <row r="550" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K550" s="5"/>
+    </row>
+    <row r="551" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K551" s="5"/>
+    </row>
+    <row r="552" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K552" s="5"/>
+    </row>
+    <row r="553" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K553" s="5"/>
+    </row>
+    <row r="554" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K554" s="5"/>
+    </row>
+    <row r="555" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K555" s="5"/>
+    </row>
+    <row r="556" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K556" s="5"/>
+    </row>
+    <row r="557" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K557" s="5"/>
+    </row>
+    <row r="558" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K558" s="5"/>
+    </row>
+    <row r="559" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K559" s="5"/>
+    </row>
+    <row r="560" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K560" s="5"/>
+    </row>
+    <row r="561" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K561" s="5"/>
+    </row>
+    <row r="562" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K562" s="5"/>
+    </row>
+    <row r="563" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K563" s="5"/>
+    </row>
+    <row r="564" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K564" s="5"/>
+    </row>
+    <row r="565" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K565" s="5"/>
+    </row>
+    <row r="566" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K566" s="5"/>
+    </row>
+    <row r="567" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K567" s="5"/>
+    </row>
+    <row r="568" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K568" s="5"/>
+    </row>
+    <row r="569" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K569" s="5"/>
+    </row>
+    <row r="570" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K570" s="5"/>
+    </row>
+    <row r="571" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K571" s="5"/>
+    </row>
+    <row r="572" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K572" s="5"/>
+    </row>
+    <row r="573" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K573" s="5"/>
+    </row>
+    <row r="574" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K574" s="5"/>
+    </row>
+    <row r="575" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K575" s="5"/>
+    </row>
+    <row r="576" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K576" s="5"/>
+    </row>
+    <row r="577" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K577" s="5"/>
+    </row>
+    <row r="578" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K578" s="5"/>
+    </row>
+    <row r="579" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K579" s="5"/>
+    </row>
+    <row r="580" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K580" s="5"/>
+    </row>
+    <row r="581" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K581" s="5"/>
+    </row>
+    <row r="582" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K582" s="5"/>
+    </row>
+    <row r="583" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K583" s="5"/>
+    </row>
+    <row r="584" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K584" s="5"/>
+    </row>
+    <row r="585" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K585" s="5"/>
+    </row>
+    <row r="586" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K586" s="5"/>
+    </row>
+    <row r="587" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K587" s="5"/>
+    </row>
+    <row r="588" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K588" s="5"/>
+    </row>
+    <row r="589" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K589" s="5"/>
+    </row>
+    <row r="590" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K590" s="5"/>
+    </row>
+    <row r="591" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K591" s="5"/>
+    </row>
+    <row r="592" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K592" s="5"/>
+    </row>
+    <row r="593" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K593" s="5"/>
+    </row>
+    <row r="594" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K594" s="5"/>
+    </row>
+    <row r="595" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K595" s="5"/>
+    </row>
+    <row r="596" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K596" s="5"/>
+    </row>
+    <row r="597" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K597" s="5"/>
+    </row>
+    <row r="598" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K598" s="5"/>
+    </row>
+    <row r="599" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K599" s="5"/>
+    </row>
+    <row r="600" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K600" s="5"/>
+    </row>
+    <row r="601" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K601" s="5"/>
+    </row>
+    <row r="602" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K602" s="5"/>
+    </row>
+    <row r="603" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K603" s="5"/>
+    </row>
+    <row r="604" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K604" s="5"/>
+    </row>
+    <row r="605" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K605" s="5"/>
+    </row>
+    <row r="606" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K606" s="5"/>
+    </row>
+    <row r="607" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K607" s="5"/>
+    </row>
+    <row r="608" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K608" s="5"/>
+    </row>
+    <row r="609" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K609" s="5"/>
+    </row>
+    <row r="610" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K610" s="5"/>
+    </row>
+    <row r="611" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K611" s="5"/>
+    </row>
+    <row r="612" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K612" s="5"/>
+    </row>
+    <row r="613" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K613" s="5"/>
+    </row>
+    <row r="614" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K614" s="5"/>
+    </row>
+    <row r="615" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K615" s="5"/>
+    </row>
+    <row r="616" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K616" s="5"/>
+    </row>
+    <row r="617" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K617" s="5"/>
+    </row>
+    <row r="618" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K618" s="5"/>
+    </row>
+    <row r="619" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K619" s="5"/>
+    </row>
+    <row r="620" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K620" s="5"/>
+    </row>
+    <row r="621" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K621" s="5"/>
+    </row>
+    <row r="622" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K622" s="5"/>
+    </row>
+    <row r="623" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K623" s="5"/>
+    </row>
+    <row r="624" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K624" s="5"/>
+    </row>
+    <row r="625" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K625" s="5"/>
+    </row>
+    <row r="626" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K626" s="5"/>
+    </row>
+    <row r="627" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K627" s="5"/>
+    </row>
+    <row r="628" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K628" s="5"/>
+    </row>
+    <row r="629" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K629" s="5"/>
+    </row>
+    <row r="630" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K630" s="5"/>
+    </row>
+    <row r="631" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K631" s="5"/>
+    </row>
+    <row r="632" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K632" s="5"/>
+    </row>
+    <row r="633" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K633" s="5"/>
+    </row>
+    <row r="634" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K634" s="5"/>
+    </row>
+    <row r="635" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K635" s="5"/>
+    </row>
+    <row r="636" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K636" s="5"/>
+    </row>
+    <row r="637" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K637" s="5"/>
+    </row>
+    <row r="638" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K638" s="5"/>
+    </row>
+    <row r="639" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K639" s="5"/>
+    </row>
+    <row r="640" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K640" s="5"/>
+    </row>
+    <row r="641" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K641" s="5"/>
+    </row>
+    <row r="642" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K642" s="5"/>
+    </row>
+    <row r="643" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K643" s="5"/>
+    </row>
+    <row r="644" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K644" s="5"/>
+    </row>
+    <row r="645" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K645" s="5"/>
+    </row>
+    <row r="646" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K646" s="5"/>
+    </row>
+    <row r="647" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K647" s="5"/>
+    </row>
+    <row r="648" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K648" s="5"/>
+    </row>
+    <row r="649" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K649" s="5"/>
+    </row>
+    <row r="650" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K650" s="5"/>
+    </row>
+    <row r="651" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K651" s="5"/>
+    </row>
+    <row r="652" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K652" s="5"/>
+    </row>
+    <row r="653" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K653" s="5"/>
+    </row>
+    <row r="654" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K654" s="5"/>
+    </row>
+    <row r="655" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K655" s="5"/>
+    </row>
+    <row r="656" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K656" s="5"/>
+    </row>
+    <row r="657" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K657" s="5"/>
+    </row>
+    <row r="658" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K658" s="5"/>
+    </row>
+    <row r="659" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K659" s="5"/>
+    </row>
+    <row r="660" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K660" s="5"/>
+    </row>
+    <row r="661" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K661" s="5"/>
+    </row>
+    <row r="662" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K662" s="5"/>
+    </row>
+    <row r="663" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K663" s="5"/>
+    </row>
+    <row r="664" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K664" s="5"/>
+    </row>
+    <row r="665" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K665" s="5"/>
+    </row>
+    <row r="666" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K666" s="5"/>
+    </row>
+    <row r="667" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K667" s="5"/>
+    </row>
+    <row r="668" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K668" s="5"/>
+    </row>
+    <row r="669" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K669" s="5"/>
+    </row>
+    <row r="670" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K670" s="5"/>
+    </row>
+    <row r="671" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K671" s="5"/>
+    </row>
+    <row r="672" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K672" s="5"/>
+    </row>
+    <row r="673" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K673" s="5"/>
+    </row>
+    <row r="674" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K674" s="5"/>
+    </row>
+    <row r="675" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K675" s="5"/>
+    </row>
+    <row r="676" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K676" s="5"/>
+    </row>
+    <row r="677" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K677" s="5"/>
+    </row>
+    <row r="678" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K678" s="5"/>
+    </row>
+    <row r="679" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K679" s="5"/>
+    </row>
+    <row r="680" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K680" s="5"/>
+    </row>
+    <row r="681" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K681" s="5"/>
+    </row>
+    <row r="682" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K682" s="5"/>
+    </row>
+    <row r="683" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K683" s="5"/>
+    </row>
+    <row r="684" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K684" s="5"/>
+    </row>
+    <row r="685" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K685" s="5"/>
+    </row>
+    <row r="686" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K686" s="5"/>
+    </row>
+    <row r="687" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K687" s="5"/>
+    </row>
+    <row r="688" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K688" s="5"/>
+    </row>
+    <row r="689" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K689" s="5"/>
+    </row>
+    <row r="690" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K690" s="5"/>
+    </row>
+    <row r="691" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K691" s="5"/>
+    </row>
+    <row r="692" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K692" s="5"/>
+    </row>
+    <row r="693" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K693" s="5"/>
+    </row>
+    <row r="694" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K694" s="5"/>
+    </row>
+    <row r="695" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K695" s="5"/>
+    </row>
+    <row r="696" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K696" s="5"/>
+    </row>
+    <row r="697" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K697" s="5"/>
+    </row>
+    <row r="698" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K698" s="5"/>
+    </row>
+    <row r="699" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K699" s="5"/>
+    </row>
+    <row r="700" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K700" s="5"/>
+    </row>
+    <row r="701" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K701" s="5"/>
+    </row>
+    <row r="702" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K702" s="5"/>
+    </row>
+    <row r="703" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K703" s="5"/>
+    </row>
+    <row r="704" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K704" s="5"/>
+    </row>
+    <row r="705" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K705" s="5"/>
+    </row>
+    <row r="706" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K706" s="5"/>
+    </row>
+    <row r="707" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K707" s="5"/>
+    </row>
+    <row r="708" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K708" s="5"/>
+    </row>
+    <row r="709" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K709" s="5"/>
+    </row>
+    <row r="710" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K710" s="5"/>
+    </row>
+    <row r="711" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K711" s="5"/>
+    </row>
+    <row r="712" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K712" s="5"/>
+    </row>
+    <row r="713" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K713" s="5"/>
+    </row>
+    <row r="714" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K714" s="5"/>
+    </row>
+    <row r="715" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K715" s="5"/>
+    </row>
+    <row r="716" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K716" s="5"/>
+    </row>
+    <row r="717" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K717" s="5"/>
+    </row>
+    <row r="718" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K718" s="5"/>
+    </row>
+    <row r="719" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K719" s="5"/>
+    </row>
+    <row r="720" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K720" s="5"/>
+    </row>
+    <row r="721" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K721" s="5"/>
+    </row>
+    <row r="722" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K722" s="5"/>
+    </row>
+    <row r="723" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K723" s="5"/>
+    </row>
+    <row r="724" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K724" s="5"/>
+    </row>
+    <row r="725" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K725" s="5"/>
+    </row>
+    <row r="726" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K726" s="5"/>
+    </row>
+    <row r="727" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K727" s="5"/>
+    </row>
+    <row r="728" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K728" s="5"/>
+    </row>
+    <row r="729" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K729" s="5"/>
+    </row>
+    <row r="730" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K730" s="5"/>
+    </row>
+    <row r="731" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K731" s="5"/>
+    </row>
+    <row r="732" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K732" s="5"/>
+    </row>
+    <row r="733" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K733" s="5"/>
+    </row>
+    <row r="734" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K734" s="5"/>
+    </row>
+    <row r="735" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K735" s="5"/>
+    </row>
+    <row r="736" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K736" s="5"/>
+    </row>
+    <row r="737" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K737" s="5"/>
+    </row>
+    <row r="738" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K738" s="5"/>
+    </row>
+    <row r="739" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K739" s="5"/>
+    </row>
+    <row r="740" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K740" s="5"/>
+    </row>
+    <row r="741" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K741" s="5"/>
+    </row>
+    <row r="742" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K742" s="5"/>
+    </row>
+    <row r="743" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K743" s="5"/>
+    </row>
+    <row r="744" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K744" s="5"/>
+    </row>
+    <row r="745" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K745" s="5"/>
+    </row>
+    <row r="746" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K746" s="5"/>
+    </row>
+    <row r="747" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K747" s="5"/>
+    </row>
+    <row r="748" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K748" s="5"/>
+    </row>
+    <row r="749" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K749" s="5"/>
+    </row>
+    <row r="750" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K750" s="5"/>
+    </row>
+    <row r="751" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K751" s="5"/>
+    </row>
+    <row r="752" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K752" s="5"/>
+    </row>
+    <row r="753" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K753" s="5"/>
+    </row>
+    <row r="754" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K754" s="5"/>
+    </row>
+    <row r="755" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K755" s="5"/>
+    </row>
+    <row r="756" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K756" s="5"/>
+    </row>
+    <row r="757" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K757" s="5"/>
+    </row>
+    <row r="758" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K758" s="5"/>
+    </row>
+    <row r="759" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K759" s="5"/>
+    </row>
+    <row r="760" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K760" s="5"/>
+    </row>
+    <row r="761" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K761" s="5"/>
+    </row>
+    <row r="762" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K762" s="5"/>
+    </row>
+    <row r="763" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K763" s="5"/>
+    </row>
+    <row r="764" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K764" s="5"/>
+    </row>
+    <row r="765" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K765" s="5"/>
+    </row>
+    <row r="766" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K766" s="5"/>
+    </row>
+    <row r="767" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K767" s="5"/>
+    </row>
+    <row r="768" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K768" s="5"/>
+    </row>
+    <row r="769" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K769" s="5"/>
+    </row>
+    <row r="770" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K770" s="5"/>
+    </row>
+    <row r="771" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K771" s="5"/>
+    </row>
+    <row r="772" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K772" s="5"/>
+    </row>
+    <row r="773" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K773" s="5"/>
+    </row>
+    <row r="774" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K774" s="5"/>
+    </row>
+    <row r="775" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K775" s="5"/>
+    </row>
+    <row r="776" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K776" s="5"/>
+    </row>
+    <row r="777" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K777" s="5"/>
+    </row>
+    <row r="778" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K778" s="5"/>
+    </row>
+    <row r="779" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K779" s="5"/>
+    </row>
+    <row r="780" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K780" s="5"/>
+    </row>
+    <row r="781" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K781" s="5"/>
+    </row>
+    <row r="782" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K782" s="5"/>
+    </row>
+    <row r="783" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K783" s="5"/>
+    </row>
+    <row r="784" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K784" s="5"/>
+    </row>
+    <row r="785" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K785" s="5"/>
+    </row>
+    <row r="786" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K786" s="5"/>
+    </row>
+    <row r="787" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K787" s="5"/>
+    </row>
+    <row r="788" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K788" s="5"/>
+    </row>
+    <row r="789" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K789" s="5"/>
+    </row>
+    <row r="790" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K790" s="5"/>
+    </row>
+    <row r="791" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K791" s="5"/>
+    </row>
+    <row r="792" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K792" s="5"/>
+    </row>
+    <row r="793" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K793" s="5"/>
+    </row>
+    <row r="794" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K794" s="5"/>
+    </row>
+    <row r="795" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K795" s="5"/>
+    </row>
+    <row r="796" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K796" s="5"/>
+    </row>
+    <row r="797" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K797" s="5"/>
+    </row>
+    <row r="798" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K798" s="5"/>
+    </row>
+    <row r="799" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K799" s="5"/>
+    </row>
+    <row r="800" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K800" s="5"/>
+    </row>
+    <row r="801" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K801" s="5"/>
+    </row>
+    <row r="802" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K802" s="5"/>
+    </row>
+    <row r="803" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K803" s="5"/>
+    </row>
+    <row r="804" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K804" s="5"/>
+    </row>
+    <row r="805" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K805" s="5"/>
+    </row>
+    <row r="806" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K806" s="5"/>
+    </row>
+    <row r="807" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K807" s="5"/>
+    </row>
+    <row r="808" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K808" s="5"/>
+    </row>
+    <row r="809" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K809" s="5"/>
+    </row>
+    <row r="810" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K810" s="5"/>
+    </row>
+    <row r="811" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K811" s="5"/>
+    </row>
+    <row r="812" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K812" s="5"/>
+    </row>
+    <row r="813" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K813" s="5"/>
+    </row>
+    <row r="814" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K814" s="5"/>
+    </row>
+    <row r="815" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K815" s="5"/>
+    </row>
+    <row r="816" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K816" s="5"/>
+    </row>
+    <row r="817" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K817" s="5"/>
+    </row>
+    <row r="818" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K818" s="5"/>
+    </row>
+    <row r="819" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K819" s="5"/>
+    </row>
+    <row r="820" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K820" s="5"/>
+    </row>
+    <row r="821" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K821" s="5"/>
+    </row>
+    <row r="822" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K822" s="5"/>
+    </row>
+    <row r="823" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K823" s="5"/>
+    </row>
+    <row r="824" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K824" s="5"/>
+    </row>
+    <row r="825" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K825" s="5"/>
+    </row>
+    <row r="826" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K826" s="5"/>
+    </row>
+    <row r="827" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K827" s="5"/>
+    </row>
+    <row r="828" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K828" s="5"/>
+    </row>
+    <row r="829" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K829" s="5"/>
+    </row>
+    <row r="830" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K830" s="5"/>
+    </row>
+    <row r="831" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K831" s="5"/>
+    </row>
+    <row r="832" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K832" s="5"/>
+    </row>
+    <row r="833" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K833" s="5"/>
+    </row>
+    <row r="834" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K834" s="5"/>
+    </row>
+    <row r="835" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K835" s="5"/>
+    </row>
+    <row r="836" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K836" s="5"/>
+    </row>
+    <row r="837" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K837" s="5"/>
+    </row>
+    <row r="838" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K838" s="5"/>
+    </row>
+    <row r="839" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K839" s="5"/>
+    </row>
+    <row r="840" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K840" s="5"/>
+    </row>
+    <row r="841" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K841" s="5"/>
+    </row>
+    <row r="842" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K842" s="5"/>
+    </row>
+    <row r="843" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K843" s="5"/>
+    </row>
+    <row r="844" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K844" s="5"/>
+    </row>
+    <row r="845" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K845" s="5"/>
+    </row>
+    <row r="846" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K846" s="5"/>
+    </row>
+    <row r="847" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K847" s="5"/>
+    </row>
+    <row r="848" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K848" s="5"/>
+    </row>
+    <row r="849" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K849" s="5"/>
+    </row>
+    <row r="850" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K850" s="5"/>
+    </row>
+    <row r="851" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K851" s="5"/>
+    </row>
+    <row r="852" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K852" s="5"/>
+    </row>
+    <row r="853" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K853" s="5"/>
+    </row>
+    <row r="854" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K854" s="5"/>
+    </row>
+    <row r="855" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K855" s="5"/>
+    </row>
+    <row r="856" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K856" s="5"/>
+    </row>
+    <row r="857" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K857" s="5"/>
+    </row>
+    <row r="858" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K858" s="5"/>
+    </row>
+    <row r="859" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K859" s="5"/>
+    </row>
+    <row r="860" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K860" s="5"/>
+    </row>
+    <row r="861" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K861" s="5"/>
+    </row>
+    <row r="862" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K862" s="5"/>
+    </row>
+    <row r="863" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K863" s="5"/>
+    </row>
+    <row r="864" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K864" s="5"/>
+    </row>
+    <row r="865" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K865" s="5"/>
+    </row>
+    <row r="866" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K866" s="5"/>
+    </row>
+    <row r="867" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K867" s="5"/>
+    </row>
+    <row r="868" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K868" s="5"/>
+    </row>
+    <row r="869" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K869" s="5"/>
+    </row>
+    <row r="870" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K870" s="5"/>
+    </row>
+    <row r="871" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K871" s="5"/>
+    </row>
+    <row r="872" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K872" s="5"/>
+    </row>
+    <row r="873" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K873" s="5"/>
+    </row>
+    <row r="874" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K874" s="5"/>
+    </row>
+    <row r="875" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K875" s="5"/>
+    </row>
+    <row r="876" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K876" s="5"/>
+    </row>
+    <row r="877" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K877" s="5"/>
+    </row>
+    <row r="878" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K878" s="5"/>
+    </row>
+    <row r="879" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K879" s="5"/>
+    </row>
+    <row r="880" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K880" s="5"/>
+    </row>
+    <row r="881" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K881" s="5"/>
+    </row>
+    <row r="882" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K882" s="5"/>
+    </row>
+    <row r="883" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K883" s="5"/>
+    </row>
+    <row r="884" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K884" s="5"/>
+    </row>
+    <row r="885" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K885" s="5"/>
+    </row>
+    <row r="886" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K886" s="5"/>
+    </row>
+    <row r="887" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K887" s="5"/>
+    </row>
+    <row r="888" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K888" s="5"/>
+    </row>
+    <row r="889" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K889" s="5"/>
+    </row>
+    <row r="890" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K890" s="5"/>
+    </row>
+    <row r="891" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K891" s="5"/>
+    </row>
+    <row r="892" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K892" s="5"/>
+    </row>
+    <row r="893" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K893" s="5"/>
+    </row>
+    <row r="894" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K894" s="5"/>
+    </row>
+    <row r="895" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K895" s="5"/>
+    </row>
+    <row r="896" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K896" s="5"/>
+    </row>
+    <row r="897" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K897" s="5"/>
+    </row>
+    <row r="898" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K898" s="5"/>
+    </row>
+    <row r="899" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K899" s="5"/>
+    </row>
+    <row r="900" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K900" s="5"/>
+    </row>
+    <row r="901" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K901" s="5"/>
+    </row>
+    <row r="902" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K902" s="5"/>
+    </row>
+    <row r="903" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K903" s="5"/>
+    </row>
+    <row r="904" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K904" s="5"/>
+    </row>
+    <row r="905" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K905" s="5"/>
+    </row>
+    <row r="906" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K906" s="5"/>
+    </row>
+    <row r="907" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K907" s="5"/>
+    </row>
+    <row r="908" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K908" s="5"/>
+    </row>
+    <row r="909" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K909" s="5"/>
+    </row>
+    <row r="910" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K910" s="5"/>
+    </row>
+    <row r="911" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K911" s="5"/>
+    </row>
+    <row r="912" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K912" s="5"/>
+    </row>
+    <row r="913" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K913" s="5"/>
+    </row>
+    <row r="914" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K914" s="5"/>
+    </row>
+    <row r="915" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K915" s="5"/>
+    </row>
+    <row r="916" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K916" s="5"/>
+    </row>
+    <row r="917" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K917" s="5"/>
+    </row>
+    <row r="918" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K918" s="5"/>
+    </row>
+    <row r="919" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K919" s="5"/>
+    </row>
+    <row r="920" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K920" s="5"/>
+    </row>
+    <row r="921" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K921" s="5"/>
+    </row>
+    <row r="922" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K922" s="5"/>
+    </row>
+    <row r="923" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K923" s="5"/>
+    </row>
+    <row r="924" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K924" s="5"/>
+    </row>
+    <row r="925" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K925" s="5"/>
+    </row>
+    <row r="926" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K926" s="5"/>
+    </row>
+    <row r="927" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K927" s="5"/>
+    </row>
+    <row r="928" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K928" s="5"/>
+    </row>
+    <row r="929" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K929" s="5"/>
+    </row>
+    <row r="930" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K930" s="5"/>
+    </row>
+    <row r="931" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K931" s="5"/>
+    </row>
+    <row r="932" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K932" s="5"/>
+    </row>
+    <row r="933" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K933" s="5"/>
+    </row>
+    <row r="934" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K934" s="5"/>
+    </row>
+    <row r="935" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K935" s="5"/>
+    </row>
+    <row r="936" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K936" s="5"/>
+    </row>
+    <row r="937" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K937" s="5"/>
+    </row>
+    <row r="938" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K938" s="5"/>
+    </row>
+    <row r="939" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K939" s="5"/>
+    </row>
+    <row r="940" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K940" s="5"/>
+    </row>
+    <row r="941" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K941" s="5"/>
+    </row>
+    <row r="942" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K942" s="5"/>
+    </row>
+    <row r="943" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K943" s="5"/>
+    </row>
+    <row r="944" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K944" s="5"/>
+    </row>
+    <row r="945" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K945" s="5"/>
+    </row>
+    <row r="946" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K946" s="5"/>
+    </row>
+    <row r="947" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K947" s="5"/>
+    </row>
+    <row r="948" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K948" s="5"/>
+    </row>
+    <row r="949" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K949" s="5"/>
+    </row>
+    <row r="950" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K950" s="5"/>
+    </row>
+    <row r="951" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K951" s="5"/>
+    </row>
+    <row r="952" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K952" s="5"/>
+    </row>
+    <row r="953" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K953" s="5"/>
+    </row>
+    <row r="954" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K954" s="5"/>
+    </row>
+    <row r="955" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K955" s="5"/>
+    </row>
+    <row r="956" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K956" s="5"/>
+    </row>
+    <row r="957" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K957" s="5"/>
+    </row>
+    <row r="958" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K958" s="5"/>
+    </row>
+    <row r="959" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K959" s="5"/>
+    </row>
+    <row r="960" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K960" s="5"/>
+    </row>
+    <row r="961" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K961" s="5"/>
+    </row>
+    <row r="962" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K962" s="5"/>
+    </row>
+    <row r="963" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K963" s="5"/>
+    </row>
+    <row r="964" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K964" s="5"/>
+    </row>
+    <row r="965" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K965" s="5"/>
+    </row>
+    <row r="966" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K966" s="5"/>
+    </row>
+    <row r="967" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K967" s="5"/>
+    </row>
+    <row r="968" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K968" s="5"/>
+    </row>
+    <row r="969" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K969" s="5"/>
+    </row>
+    <row r="970" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K970" s="5"/>
+    </row>
+    <row r="971" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K971" s="5"/>
+    </row>
+    <row r="972" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K972" s="5"/>
+    </row>
+    <row r="973" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K973" s="5"/>
+    </row>
+    <row r="974" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K974" s="5"/>
+    </row>
+    <row r="975" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K975" s="5"/>
+    </row>
+    <row r="976" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K976" s="5"/>
+    </row>
+    <row r="977" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K977" s="5"/>
+    </row>
+    <row r="978" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K978" s="5"/>
+    </row>
+    <row r="979" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K979" s="5"/>
+    </row>
+    <row r="980" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K980" s="5"/>
+    </row>
+    <row r="981" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K981" s="5"/>
+    </row>
+    <row r="982" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K982" s="5"/>
+    </row>
+    <row r="983" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K983" s="5"/>
+    </row>
+    <row r="984" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K984" s="5"/>
+    </row>
+    <row r="985" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K985" s="5"/>
+    </row>
+    <row r="986" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K986" s="5"/>
+    </row>
+    <row r="987" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K987" s="5"/>
+    </row>
+    <row r="988" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K988" s="5"/>
+    </row>
+    <row r="989" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K989" s="5"/>
+    </row>
+    <row r="990" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K990" s="5"/>
+    </row>
+    <row r="991" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K991" s="5"/>
+    </row>
+    <row r="992" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K992" s="5"/>
+    </row>
+    <row r="993" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K993" s="5"/>
+    </row>
+    <row r="994" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K994" s="5"/>
+    </row>
+    <row r="995" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K995" s="5"/>
+    </row>
+    <row r="996" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K996" s="5"/>
+    </row>
+    <row r="997" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K997" s="5"/>
+    </row>
+    <row r="998" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K998" s="5"/>
+    </row>
+    <row r="999" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K999" s="5"/>
+    </row>
+    <row r="1000" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1000" s="5"/>
+    </row>
+    <row r="1001" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1001" s="5"/>
+    </row>
+    <row r="1002" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1002" s="5"/>
+    </row>
+    <row r="1003" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K1003" s="5"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K1003" type="list">
+      <formula1>"NA,Cumulate,Forward fill,Compute"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -446,5 +3537,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/sample_uploads/investor_kpi_mappings_update.xlsx
+++ b/public/sample_uploads/investor_kpi_mappings_update.xlsx
@@ -43,12 +43,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Optional, input when Auto Fill is selected as Compute
 </t>
@@ -60,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t xml:space="preserve">Stakeholder</t>
   </si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t xml:space="preserve">Update Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denomination</t>
   </si>
   <si>
     <t xml:space="preserve">Demo Fund Company</t>
@@ -144,7 +144,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -183,14 +183,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -263,11 +255,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -395,7 +387,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1003"/>
+  <dimension ref="A1:N1003"/>
   <sheetFormatPr defaultColWidth="9.47265625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.93"/>
@@ -408,7 +400,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="21.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -445,35 +437,38 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
@@ -481,34 +476,34 @@
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="M2" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
@@ -516,3012 +511,3012 @@
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="M3" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K4" s="5"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K5" s="5"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K6" s="5"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K7" s="5"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K8" s="5"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K9" s="5"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K10" s="5"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K11" s="5"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K12" s="5"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K13" s="5"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K14" s="5"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K15" s="5"/>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K16" s="5"/>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K17" s="5"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K18" s="5"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K19" s="5"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K20" s="5"/>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K21" s="5"/>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K22" s="5"/>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K23" s="5"/>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K24" s="5"/>
+      <c r="K24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K25" s="5"/>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K26" s="5"/>
+      <c r="K26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K27" s="5"/>
+      <c r="K27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K28" s="5"/>
+      <c r="K28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K29" s="5"/>
+      <c r="K29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K30" s="5"/>
+      <c r="K30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K31" s="5"/>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K32" s="5"/>
+      <c r="K32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K33" s="5"/>
+      <c r="K33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K34" s="5"/>
+      <c r="K34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K35" s="5"/>
+      <c r="K35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K36" s="5"/>
+      <c r="K36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K37" s="5"/>
+      <c r="K37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K38" s="5"/>
+      <c r="K38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K39" s="5"/>
+      <c r="K39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K40" s="5"/>
+      <c r="K40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K41" s="5"/>
+      <c r="K41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K42" s="5"/>
+      <c r="K42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K43" s="5"/>
+      <c r="K43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K44" s="5"/>
+      <c r="K44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K45" s="5"/>
+      <c r="K45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K46" s="5"/>
+      <c r="K46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K47" s="5"/>
+      <c r="K47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K48" s="5"/>
+      <c r="K48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K49" s="5"/>
+      <c r="K49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K50" s="5"/>
+      <c r="K50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K51" s="5"/>
+      <c r="K51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K52" s="5"/>
+      <c r="K52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K53" s="5"/>
+      <c r="K53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K54" s="5"/>
+      <c r="K54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K55" s="5"/>
+      <c r="K55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K56" s="5"/>
+      <c r="K56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K57" s="5"/>
+      <c r="K57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K58" s="5"/>
+      <c r="K58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K59" s="5"/>
+      <c r="K59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K60" s="5"/>
+      <c r="K60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K61" s="5"/>
+      <c r="K61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K62" s="5"/>
+      <c r="K62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K63" s="5"/>
+      <c r="K63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K64" s="5"/>
+      <c r="K64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K65" s="5"/>
+      <c r="K65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K66" s="5"/>
+      <c r="K66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K67" s="5"/>
+      <c r="K67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K68" s="5"/>
+      <c r="K68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K69" s="5"/>
+      <c r="K69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K70" s="5"/>
+      <c r="K70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K71" s="5"/>
+      <c r="K71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K72" s="5"/>
+      <c r="K72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K73" s="5"/>
+      <c r="K73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K74" s="5"/>
+      <c r="K74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K75" s="5"/>
+      <c r="K75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K76" s="5"/>
+      <c r="K76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K77" s="5"/>
+      <c r="K77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K78" s="5"/>
+      <c r="K78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K79" s="5"/>
+      <c r="K79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K80" s="5"/>
+      <c r="K80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K81" s="5"/>
+      <c r="K81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K82" s="5"/>
+      <c r="K82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K83" s="5"/>
+      <c r="K83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K84" s="5"/>
+      <c r="K84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K85" s="5"/>
+      <c r="K85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K86" s="5"/>
+      <c r="K86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K87" s="5"/>
+      <c r="K87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K88" s="5"/>
+      <c r="K88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K89" s="5"/>
+      <c r="K89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K90" s="5"/>
+      <c r="K90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K91" s="5"/>
+      <c r="K91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K92" s="5"/>
+      <c r="K92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K93" s="5"/>
+      <c r="K93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K94" s="5"/>
+      <c r="K94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K95" s="5"/>
+      <c r="K95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K96" s="5"/>
+      <c r="K96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K97" s="5"/>
+      <c r="K97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K98" s="5"/>
+      <c r="K98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K99" s="5"/>
+      <c r="K99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K100" s="5"/>
+      <c r="K100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K101" s="5"/>
+      <c r="K101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K102" s="5"/>
+      <c r="K102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K103" s="5"/>
+      <c r="K103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K104" s="5"/>
+      <c r="K104" s="4"/>
     </row>
     <row r="105" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K105" s="5"/>
+      <c r="K105" s="4"/>
     </row>
     <row r="106" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K106" s="5"/>
+      <c r="K106" s="4"/>
     </row>
     <row r="107" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K107" s="5"/>
+      <c r="K107" s="4"/>
     </row>
     <row r="108" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K108" s="5"/>
+      <c r="K108" s="4"/>
     </row>
     <row r="109" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K109" s="5"/>
+      <c r="K109" s="4"/>
     </row>
     <row r="110" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K110" s="5"/>
+      <c r="K110" s="4"/>
     </row>
     <row r="111" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K111" s="5"/>
+      <c r="K111" s="4"/>
     </row>
     <row r="112" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K112" s="5"/>
+      <c r="K112" s="4"/>
     </row>
     <row r="113" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K113" s="5"/>
+      <c r="K113" s="4"/>
     </row>
     <row r="114" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K114" s="5"/>
+      <c r="K114" s="4"/>
     </row>
     <row r="115" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K115" s="5"/>
+      <c r="K115" s="4"/>
     </row>
     <row r="116" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K116" s="5"/>
+      <c r="K116" s="4"/>
     </row>
     <row r="117" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K117" s="5"/>
+      <c r="K117" s="4"/>
     </row>
     <row r="118" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K118" s="5"/>
+      <c r="K118" s="4"/>
     </row>
     <row r="119" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K119" s="5"/>
+      <c r="K119" s="4"/>
     </row>
     <row r="120" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K120" s="5"/>
+      <c r="K120" s="4"/>
     </row>
     <row r="121" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K121" s="5"/>
+      <c r="K121" s="4"/>
     </row>
     <row r="122" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K122" s="5"/>
+      <c r="K122" s="4"/>
     </row>
     <row r="123" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K123" s="5"/>
+      <c r="K123" s="4"/>
     </row>
     <row r="124" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K124" s="5"/>
+      <c r="K124" s="4"/>
     </row>
     <row r="125" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K125" s="5"/>
+      <c r="K125" s="4"/>
     </row>
     <row r="126" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K126" s="5"/>
+      <c r="K126" s="4"/>
     </row>
     <row r="127" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K127" s="5"/>
+      <c r="K127" s="4"/>
     </row>
     <row r="128" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K128" s="5"/>
+      <c r="K128" s="4"/>
     </row>
     <row r="129" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K129" s="5"/>
+      <c r="K129" s="4"/>
     </row>
     <row r="130" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K130" s="5"/>
+      <c r="K130" s="4"/>
     </row>
     <row r="131" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K131" s="5"/>
+      <c r="K131" s="4"/>
     </row>
     <row r="132" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K132" s="5"/>
+      <c r="K132" s="4"/>
     </row>
     <row r="133" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K133" s="5"/>
+      <c r="K133" s="4"/>
     </row>
     <row r="134" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K134" s="5"/>
+      <c r="K134" s="4"/>
     </row>
     <row r="135" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K135" s="5"/>
+      <c r="K135" s="4"/>
     </row>
     <row r="136" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K136" s="5"/>
+      <c r="K136" s="4"/>
     </row>
     <row r="137" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K137" s="5"/>
+      <c r="K137" s="4"/>
     </row>
     <row r="138" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K138" s="5"/>
+      <c r="K138" s="4"/>
     </row>
     <row r="139" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K139" s="5"/>
+      <c r="K139" s="4"/>
     </row>
     <row r="140" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K140" s="5"/>
+      <c r="K140" s="4"/>
     </row>
     <row r="141" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K141" s="5"/>
+      <c r="K141" s="4"/>
     </row>
     <row r="142" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K142" s="5"/>
+      <c r="K142" s="4"/>
     </row>
     <row r="143" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K143" s="5"/>
+      <c r="K143" s="4"/>
     </row>
     <row r="144" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K144" s="5"/>
+      <c r="K144" s="4"/>
     </row>
     <row r="145" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K145" s="5"/>
+      <c r="K145" s="4"/>
     </row>
     <row r="146" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K146" s="5"/>
+      <c r="K146" s="4"/>
     </row>
     <row r="147" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K147" s="5"/>
+      <c r="K147" s="4"/>
     </row>
     <row r="148" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K148" s="5"/>
+      <c r="K148" s="4"/>
     </row>
     <row r="149" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K149" s="5"/>
+      <c r="K149" s="4"/>
     </row>
     <row r="150" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K150" s="5"/>
+      <c r="K150" s="4"/>
     </row>
     <row r="151" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K151" s="5"/>
+      <c r="K151" s="4"/>
     </row>
     <row r="152" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K152" s="5"/>
+      <c r="K152" s="4"/>
     </row>
     <row r="153" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K153" s="5"/>
+      <c r="K153" s="4"/>
     </row>
     <row r="154" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K154" s="5"/>
+      <c r="K154" s="4"/>
     </row>
     <row r="155" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K155" s="5"/>
+      <c r="K155" s="4"/>
     </row>
     <row r="156" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K156" s="5"/>
+      <c r="K156" s="4"/>
     </row>
     <row r="157" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K157" s="5"/>
+      <c r="K157" s="4"/>
     </row>
     <row r="158" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K158" s="5"/>
+      <c r="K158" s="4"/>
     </row>
     <row r="159" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K159" s="5"/>
+      <c r="K159" s="4"/>
     </row>
     <row r="160" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K160" s="5"/>
+      <c r="K160" s="4"/>
     </row>
     <row r="161" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K161" s="5"/>
+      <c r="K161" s="4"/>
     </row>
     <row r="162" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K162" s="5"/>
+      <c r="K162" s="4"/>
     </row>
     <row r="163" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K163" s="5"/>
+      <c r="K163" s="4"/>
     </row>
     <row r="164" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K164" s="5"/>
+      <c r="K164" s="4"/>
     </row>
     <row r="165" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K165" s="5"/>
+      <c r="K165" s="4"/>
     </row>
     <row r="166" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K166" s="5"/>
+      <c r="K166" s="4"/>
     </row>
     <row r="167" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K167" s="5"/>
+      <c r="K167" s="4"/>
     </row>
     <row r="168" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K168" s="5"/>
+      <c r="K168" s="4"/>
     </row>
     <row r="169" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K169" s="5"/>
+      <c r="K169" s="4"/>
     </row>
     <row r="170" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K170" s="5"/>
+      <c r="K170" s="4"/>
     </row>
     <row r="171" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K171" s="5"/>
+      <c r="K171" s="4"/>
     </row>
     <row r="172" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K172" s="5"/>
+      <c r="K172" s="4"/>
     </row>
     <row r="173" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K173" s="5"/>
+      <c r="K173" s="4"/>
     </row>
     <row r="174" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K174" s="5"/>
+      <c r="K174" s="4"/>
     </row>
     <row r="175" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K175" s="5"/>
+      <c r="K175" s="4"/>
     </row>
     <row r="176" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K176" s="5"/>
+      <c r="K176" s="4"/>
     </row>
     <row r="177" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K177" s="5"/>
+      <c r="K177" s="4"/>
     </row>
     <row r="178" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K178" s="5"/>
+      <c r="K178" s="4"/>
     </row>
     <row r="179" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K179" s="5"/>
+      <c r="K179" s="4"/>
     </row>
     <row r="180" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K180" s="5"/>
+      <c r="K180" s="4"/>
     </row>
     <row r="181" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K181" s="5"/>
+      <c r="K181" s="4"/>
     </row>
     <row r="182" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K182" s="5"/>
+      <c r="K182" s="4"/>
     </row>
     <row r="183" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K183" s="5"/>
+      <c r="K183" s="4"/>
     </row>
     <row r="184" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K184" s="5"/>
+      <c r="K184" s="4"/>
     </row>
     <row r="185" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K185" s="5"/>
+      <c r="K185" s="4"/>
     </row>
     <row r="186" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K186" s="5"/>
+      <c r="K186" s="4"/>
     </row>
     <row r="187" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K187" s="5"/>
+      <c r="K187" s="4"/>
     </row>
     <row r="188" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K188" s="5"/>
+      <c r="K188" s="4"/>
     </row>
     <row r="189" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K189" s="5"/>
+      <c r="K189" s="4"/>
     </row>
     <row r="190" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K190" s="5"/>
+      <c r="K190" s="4"/>
     </row>
     <row r="191" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K191" s="5"/>
+      <c r="K191" s="4"/>
     </row>
     <row r="192" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K192" s="5"/>
+      <c r="K192" s="4"/>
     </row>
     <row r="193" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K193" s="5"/>
+      <c r="K193" s="4"/>
     </row>
     <row r="194" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K194" s="5"/>
+      <c r="K194" s="4"/>
     </row>
     <row r="195" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K195" s="5"/>
+      <c r="K195" s="4"/>
     </row>
     <row r="196" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K196" s="5"/>
+      <c r="K196" s="4"/>
     </row>
     <row r="197" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K197" s="5"/>
+      <c r="K197" s="4"/>
     </row>
     <row r="198" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K198" s="5"/>
+      <c r="K198" s="4"/>
     </row>
     <row r="199" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K199" s="5"/>
+      <c r="K199" s="4"/>
     </row>
     <row r="200" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K200" s="5"/>
+      <c r="K200" s="4"/>
     </row>
     <row r="201" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K201" s="5"/>
+      <c r="K201" s="4"/>
     </row>
     <row r="202" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K202" s="5"/>
+      <c r="K202" s="4"/>
     </row>
     <row r="203" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K203" s="5"/>
+      <c r="K203" s="4"/>
     </row>
     <row r="204" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K204" s="5"/>
+      <c r="K204" s="4"/>
     </row>
     <row r="205" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K205" s="5"/>
+      <c r="K205" s="4"/>
     </row>
     <row r="206" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K206" s="5"/>
+      <c r="K206" s="4"/>
     </row>
     <row r="207" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K207" s="5"/>
+      <c r="K207" s="4"/>
     </row>
     <row r="208" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K208" s="5"/>
+      <c r="K208" s="4"/>
     </row>
     <row r="209" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K209" s="5"/>
+      <c r="K209" s="4"/>
     </row>
     <row r="210" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K210" s="5"/>
+      <c r="K210" s="4"/>
     </row>
     <row r="211" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K211" s="5"/>
+      <c r="K211" s="4"/>
     </row>
     <row r="212" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K212" s="5"/>
+      <c r="K212" s="4"/>
     </row>
     <row r="213" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K213" s="5"/>
+      <c r="K213" s="4"/>
     </row>
     <row r="214" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K214" s="5"/>
+      <c r="K214" s="4"/>
     </row>
     <row r="215" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K215" s="5"/>
+      <c r="K215" s="4"/>
     </row>
     <row r="216" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K216" s="5"/>
+      <c r="K216" s="4"/>
     </row>
     <row r="217" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K217" s="5"/>
+      <c r="K217" s="4"/>
     </row>
     <row r="218" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K218" s="5"/>
+      <c r="K218" s="4"/>
     </row>
     <row r="219" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K219" s="5"/>
+      <c r="K219" s="4"/>
     </row>
     <row r="220" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K220" s="5"/>
+      <c r="K220" s="4"/>
     </row>
     <row r="221" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K221" s="5"/>
+      <c r="K221" s="4"/>
     </row>
     <row r="222" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K222" s="5"/>
+      <c r="K222" s="4"/>
     </row>
     <row r="223" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K223" s="5"/>
+      <c r="K223" s="4"/>
     </row>
     <row r="224" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K224" s="5"/>
+      <c r="K224" s="4"/>
     </row>
     <row r="225" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K225" s="5"/>
+      <c r="K225" s="4"/>
     </row>
     <row r="226" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K226" s="5"/>
+      <c r="K226" s="4"/>
     </row>
     <row r="227" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K227" s="5"/>
+      <c r="K227" s="4"/>
     </row>
     <row r="228" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K228" s="5"/>
+      <c r="K228" s="4"/>
     </row>
     <row r="229" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K229" s="5"/>
+      <c r="K229" s="4"/>
     </row>
     <row r="230" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K230" s="5"/>
+      <c r="K230" s="4"/>
     </row>
     <row r="231" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K231" s="5"/>
+      <c r="K231" s="4"/>
     </row>
     <row r="232" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K232" s="5"/>
+      <c r="K232" s="4"/>
     </row>
     <row r="233" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K233" s="5"/>
+      <c r="K233" s="4"/>
     </row>
     <row r="234" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K234" s="5"/>
+      <c r="K234" s="4"/>
     </row>
     <row r="235" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K235" s="5"/>
+      <c r="K235" s="4"/>
     </row>
     <row r="236" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K236" s="5"/>
+      <c r="K236" s="4"/>
     </row>
     <row r="237" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K237" s="5"/>
+      <c r="K237" s="4"/>
     </row>
     <row r="238" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K238" s="5"/>
+      <c r="K238" s="4"/>
     </row>
     <row r="239" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K239" s="5"/>
+      <c r="K239" s="4"/>
     </row>
     <row r="240" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K240" s="5"/>
+      <c r="K240" s="4"/>
     </row>
     <row r="241" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K241" s="5"/>
+      <c r="K241" s="4"/>
     </row>
     <row r="242" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K242" s="5"/>
+      <c r="K242" s="4"/>
     </row>
     <row r="243" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K243" s="5"/>
+      <c r="K243" s="4"/>
     </row>
     <row r="244" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K244" s="5"/>
+      <c r="K244" s="4"/>
     </row>
     <row r="245" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K245" s="5"/>
+      <c r="K245" s="4"/>
     </row>
     <row r="246" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K246" s="5"/>
+      <c r="K246" s="4"/>
     </row>
     <row r="247" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K247" s="5"/>
+      <c r="K247" s="4"/>
     </row>
     <row r="248" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K248" s="5"/>
+      <c r="K248" s="4"/>
     </row>
     <row r="249" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K249" s="5"/>
+      <c r="K249" s="4"/>
     </row>
     <row r="250" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K250" s="5"/>
+      <c r="K250" s="4"/>
     </row>
     <row r="251" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K251" s="5"/>
+      <c r="K251" s="4"/>
     </row>
     <row r="252" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K252" s="5"/>
+      <c r="K252" s="4"/>
     </row>
     <row r="253" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K253" s="5"/>
+      <c r="K253" s="4"/>
     </row>
     <row r="254" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K254" s="5"/>
+      <c r="K254" s="4"/>
     </row>
     <row r="255" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K255" s="5"/>
+      <c r="K255" s="4"/>
     </row>
     <row r="256" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K256" s="5"/>
+      <c r="K256" s="4"/>
     </row>
     <row r="257" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K257" s="5"/>
+      <c r="K257" s="4"/>
     </row>
     <row r="258" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K258" s="5"/>
+      <c r="K258" s="4"/>
     </row>
     <row r="259" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K259" s="5"/>
+      <c r="K259" s="4"/>
     </row>
     <row r="260" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K260" s="5"/>
+      <c r="K260" s="4"/>
     </row>
     <row r="261" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K261" s="5"/>
+      <c r="K261" s="4"/>
     </row>
     <row r="262" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K262" s="5"/>
+      <c r="K262" s="4"/>
     </row>
     <row r="263" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K263" s="5"/>
+      <c r="K263" s="4"/>
     </row>
     <row r="264" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K264" s="5"/>
+      <c r="K264" s="4"/>
     </row>
     <row r="265" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K265" s="5"/>
+      <c r="K265" s="4"/>
     </row>
     <row r="266" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K266" s="5"/>
+      <c r="K266" s="4"/>
     </row>
     <row r="267" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K267" s="5"/>
+      <c r="K267" s="4"/>
     </row>
     <row r="268" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K268" s="5"/>
+      <c r="K268" s="4"/>
     </row>
     <row r="269" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K269" s="5"/>
+      <c r="K269" s="4"/>
     </row>
     <row r="270" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K270" s="5"/>
+      <c r="K270" s="4"/>
     </row>
     <row r="271" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K271" s="5"/>
+      <c r="K271" s="4"/>
     </row>
     <row r="272" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K272" s="5"/>
+      <c r="K272" s="4"/>
     </row>
     <row r="273" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K273" s="5"/>
+      <c r="K273" s="4"/>
     </row>
     <row r="274" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K274" s="5"/>
+      <c r="K274" s="4"/>
     </row>
     <row r="275" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K275" s="5"/>
+      <c r="K275" s="4"/>
     </row>
     <row r="276" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K276" s="5"/>
+      <c r="K276" s="4"/>
     </row>
     <row r="277" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K277" s="5"/>
+      <c r="K277" s="4"/>
     </row>
     <row r="278" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K278" s="5"/>
+      <c r="K278" s="4"/>
     </row>
     <row r="279" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K279" s="5"/>
+      <c r="K279" s="4"/>
     </row>
     <row r="280" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K280" s="5"/>
+      <c r="K280" s="4"/>
     </row>
     <row r="281" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K281" s="5"/>
+      <c r="K281" s="4"/>
     </row>
     <row r="282" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K282" s="5"/>
+      <c r="K282" s="4"/>
     </row>
     <row r="283" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K283" s="5"/>
+      <c r="K283" s="4"/>
     </row>
     <row r="284" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K284" s="5"/>
+      <c r="K284" s="4"/>
     </row>
     <row r="285" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K285" s="5"/>
+      <c r="K285" s="4"/>
     </row>
     <row r="286" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K286" s="5"/>
+      <c r="K286" s="4"/>
     </row>
     <row r="287" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K287" s="5"/>
+      <c r="K287" s="4"/>
     </row>
     <row r="288" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K288" s="5"/>
+      <c r="K288" s="4"/>
     </row>
     <row r="289" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K289" s="5"/>
+      <c r="K289" s="4"/>
     </row>
     <row r="290" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K290" s="5"/>
+      <c r="K290" s="4"/>
     </row>
     <row r="291" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K291" s="5"/>
+      <c r="K291" s="4"/>
     </row>
     <row r="292" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K292" s="5"/>
+      <c r="K292" s="4"/>
     </row>
     <row r="293" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K293" s="5"/>
+      <c r="K293" s="4"/>
     </row>
     <row r="294" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K294" s="5"/>
+      <c r="K294" s="4"/>
     </row>
     <row r="295" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K295" s="5"/>
+      <c r="K295" s="4"/>
     </row>
     <row r="296" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K296" s="5"/>
+      <c r="K296" s="4"/>
     </row>
     <row r="297" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K297" s="5"/>
+      <c r="K297" s="4"/>
     </row>
     <row r="298" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K298" s="5"/>
+      <c r="K298" s="4"/>
     </row>
     <row r="299" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K299" s="5"/>
+      <c r="K299" s="4"/>
     </row>
     <row r="300" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K300" s="5"/>
+      <c r="K300" s="4"/>
     </row>
     <row r="301" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K301" s="5"/>
+      <c r="K301" s="4"/>
     </row>
     <row r="302" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K302" s="5"/>
+      <c r="K302" s="4"/>
     </row>
     <row r="303" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K303" s="5"/>
+      <c r="K303" s="4"/>
     </row>
     <row r="304" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K304" s="5"/>
+      <c r="K304" s="4"/>
     </row>
     <row r="305" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K305" s="5"/>
+      <c r="K305" s="4"/>
     </row>
     <row r="306" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K306" s="5"/>
+      <c r="K306" s="4"/>
     </row>
     <row r="307" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K307" s="5"/>
+      <c r="K307" s="4"/>
     </row>
     <row r="308" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K308" s="5"/>
+      <c r="K308" s="4"/>
     </row>
     <row r="309" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K309" s="5"/>
+      <c r="K309" s="4"/>
     </row>
     <row r="310" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K310" s="5"/>
+      <c r="K310" s="4"/>
     </row>
     <row r="311" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K311" s="5"/>
+      <c r="K311" s="4"/>
     </row>
     <row r="312" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K312" s="5"/>
+      <c r="K312" s="4"/>
     </row>
     <row r="313" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K313" s="5"/>
+      <c r="K313" s="4"/>
     </row>
     <row r="314" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K314" s="5"/>
+      <c r="K314" s="4"/>
     </row>
     <row r="315" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K315" s="5"/>
+      <c r="K315" s="4"/>
     </row>
     <row r="316" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K316" s="5"/>
+      <c r="K316" s="4"/>
     </row>
     <row r="317" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K317" s="5"/>
+      <c r="K317" s="4"/>
     </row>
     <row r="318" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K318" s="5"/>
+      <c r="K318" s="4"/>
     </row>
     <row r="319" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K319" s="5"/>
+      <c r="K319" s="4"/>
     </row>
     <row r="320" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K320" s="5"/>
+      <c r="K320" s="4"/>
     </row>
     <row r="321" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K321" s="5"/>
+      <c r="K321" s="4"/>
     </row>
     <row r="322" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K322" s="5"/>
+      <c r="K322" s="4"/>
     </row>
     <row r="323" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K323" s="5"/>
+      <c r="K323" s="4"/>
     </row>
     <row r="324" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K324" s="5"/>
+      <c r="K324" s="4"/>
     </row>
     <row r="325" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K325" s="5"/>
+      <c r="K325" s="4"/>
     </row>
     <row r="326" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K326" s="5"/>
+      <c r="K326" s="4"/>
     </row>
     <row r="327" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K327" s="5"/>
+      <c r="K327" s="4"/>
     </row>
     <row r="328" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K328" s="5"/>
+      <c r="K328" s="4"/>
     </row>
     <row r="329" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K329" s="5"/>
+      <c r="K329" s="4"/>
     </row>
     <row r="330" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K330" s="5"/>
+      <c r="K330" s="4"/>
     </row>
     <row r="331" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K331" s="5"/>
+      <c r="K331" s="4"/>
     </row>
     <row r="332" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K332" s="5"/>
+      <c r="K332" s="4"/>
     </row>
     <row r="333" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K333" s="5"/>
+      <c r="K333" s="4"/>
     </row>
     <row r="334" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K334" s="5"/>
+      <c r="K334" s="4"/>
     </row>
     <row r="335" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K335" s="5"/>
+      <c r="K335" s="4"/>
     </row>
     <row r="336" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K336" s="5"/>
+      <c r="K336" s="4"/>
     </row>
     <row r="337" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K337" s="5"/>
+      <c r="K337" s="4"/>
     </row>
     <row r="338" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K338" s="5"/>
+      <c r="K338" s="4"/>
     </row>
     <row r="339" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K339" s="5"/>
+      <c r="K339" s="4"/>
     </row>
     <row r="340" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K340" s="5"/>
+      <c r="K340" s="4"/>
     </row>
     <row r="341" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K341" s="5"/>
+      <c r="K341" s="4"/>
     </row>
     <row r="342" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K342" s="5"/>
+      <c r="K342" s="4"/>
     </row>
     <row r="343" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K343" s="5"/>
+      <c r="K343" s="4"/>
     </row>
     <row r="344" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K344" s="5"/>
+      <c r="K344" s="4"/>
     </row>
     <row r="345" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K345" s="5"/>
+      <c r="K345" s="4"/>
     </row>
     <row r="346" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K346" s="5"/>
+      <c r="K346" s="4"/>
     </row>
     <row r="347" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K347" s="5"/>
+      <c r="K347" s="4"/>
     </row>
     <row r="348" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K348" s="5"/>
+      <c r="K348" s="4"/>
     </row>
     <row r="349" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K349" s="5"/>
+      <c r="K349" s="4"/>
     </row>
     <row r="350" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K350" s="5"/>
+      <c r="K350" s="4"/>
     </row>
     <row r="351" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K351" s="5"/>
+      <c r="K351" s="4"/>
     </row>
     <row r="352" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K352" s="5"/>
+      <c r="K352" s="4"/>
     </row>
     <row r="353" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K353" s="5"/>
+      <c r="K353" s="4"/>
     </row>
     <row r="354" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K354" s="5"/>
+      <c r="K354" s="4"/>
     </row>
     <row r="355" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K355" s="5"/>
+      <c r="K355" s="4"/>
     </row>
     <row r="356" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K356" s="5"/>
+      <c r="K356" s="4"/>
     </row>
     <row r="357" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K357" s="5"/>
+      <c r="K357" s="4"/>
     </row>
     <row r="358" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K358" s="5"/>
+      <c r="K358" s="4"/>
     </row>
     <row r="359" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K359" s="5"/>
+      <c r="K359" s="4"/>
     </row>
     <row r="360" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K360" s="5"/>
+      <c r="K360" s="4"/>
     </row>
     <row r="361" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K361" s="5"/>
+      <c r="K361" s="4"/>
     </row>
     <row r="362" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K362" s="5"/>
+      <c r="K362" s="4"/>
     </row>
     <row r="363" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K363" s="5"/>
+      <c r="K363" s="4"/>
     </row>
     <row r="364" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K364" s="5"/>
+      <c r="K364" s="4"/>
     </row>
     <row r="365" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K365" s="5"/>
+      <c r="K365" s="4"/>
     </row>
     <row r="366" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K366" s="5"/>
+      <c r="K366" s="4"/>
     </row>
     <row r="367" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K367" s="5"/>
+      <c r="K367" s="4"/>
     </row>
     <row r="368" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K368" s="5"/>
+      <c r="K368" s="4"/>
     </row>
     <row r="369" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K369" s="5"/>
+      <c r="K369" s="4"/>
     </row>
     <row r="370" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K370" s="5"/>
+      <c r="K370" s="4"/>
     </row>
     <row r="371" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K371" s="5"/>
+      <c r="K371" s="4"/>
     </row>
     <row r="372" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K372" s="5"/>
+      <c r="K372" s="4"/>
     </row>
     <row r="373" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K373" s="5"/>
+      <c r="K373" s="4"/>
     </row>
     <row r="374" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K374" s="5"/>
+      <c r="K374" s="4"/>
     </row>
     <row r="375" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K375" s="5"/>
+      <c r="K375" s="4"/>
     </row>
     <row r="376" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K376" s="5"/>
+      <c r="K376" s="4"/>
     </row>
     <row r="377" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K377" s="5"/>
+      <c r="K377" s="4"/>
     </row>
     <row r="378" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K378" s="5"/>
+      <c r="K378" s="4"/>
     </row>
     <row r="379" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K379" s="5"/>
+      <c r="K379" s="4"/>
     </row>
     <row r="380" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K380" s="5"/>
+      <c r="K380" s="4"/>
     </row>
     <row r="381" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K381" s="5"/>
+      <c r="K381" s="4"/>
     </row>
     <row r="382" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K382" s="5"/>
+      <c r="K382" s="4"/>
     </row>
     <row r="383" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K383" s="5"/>
+      <c r="K383" s="4"/>
     </row>
     <row r="384" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K384" s="5"/>
+      <c r="K384" s="4"/>
     </row>
     <row r="385" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K385" s="5"/>
+      <c r="K385" s="4"/>
     </row>
     <row r="386" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K386" s="5"/>
+      <c r="K386" s="4"/>
     </row>
     <row r="387" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K387" s="5"/>
+      <c r="K387" s="4"/>
     </row>
     <row r="388" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K388" s="5"/>
+      <c r="K388" s="4"/>
     </row>
     <row r="389" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K389" s="5"/>
+      <c r="K389" s="4"/>
     </row>
     <row r="390" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K390" s="5"/>
+      <c r="K390" s="4"/>
     </row>
     <row r="391" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K391" s="5"/>
+      <c r="K391" s="4"/>
     </row>
     <row r="392" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K392" s="5"/>
+      <c r="K392" s="4"/>
     </row>
     <row r="393" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K393" s="5"/>
+      <c r="K393" s="4"/>
     </row>
     <row r="394" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K394" s="5"/>
+      <c r="K394" s="4"/>
     </row>
     <row r="395" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K395" s="5"/>
+      <c r="K395" s="4"/>
     </row>
     <row r="396" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K396" s="5"/>
+      <c r="K396" s="4"/>
     </row>
     <row r="397" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K397" s="5"/>
+      <c r="K397" s="4"/>
     </row>
     <row r="398" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K398" s="5"/>
+      <c r="K398" s="4"/>
     </row>
     <row r="399" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K399" s="5"/>
+      <c r="K399" s="4"/>
     </row>
     <row r="400" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K400" s="5"/>
+      <c r="K400" s="4"/>
     </row>
     <row r="401" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K401" s="5"/>
+      <c r="K401" s="4"/>
     </row>
     <row r="402" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K402" s="5"/>
+      <c r="K402" s="4"/>
     </row>
     <row r="403" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K403" s="5"/>
+      <c r="K403" s="4"/>
     </row>
     <row r="404" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K404" s="5"/>
+      <c r="K404" s="4"/>
     </row>
     <row r="405" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K405" s="5"/>
+      <c r="K405" s="4"/>
     </row>
     <row r="406" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K406" s="5"/>
+      <c r="K406" s="4"/>
     </row>
     <row r="407" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K407" s="5"/>
+      <c r="K407" s="4"/>
     </row>
     <row r="408" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K408" s="5"/>
+      <c r="K408" s="4"/>
     </row>
     <row r="409" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K409" s="5"/>
+      <c r="K409" s="4"/>
     </row>
     <row r="410" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K410" s="5"/>
+      <c r="K410" s="4"/>
     </row>
     <row r="411" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K411" s="5"/>
+      <c r="K411" s="4"/>
     </row>
     <row r="412" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K412" s="5"/>
+      <c r="K412" s="4"/>
     </row>
     <row r="413" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K413" s="5"/>
+      <c r="K413" s="4"/>
     </row>
     <row r="414" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K414" s="5"/>
+      <c r="K414" s="4"/>
     </row>
     <row r="415" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K415" s="5"/>
+      <c r="K415" s="4"/>
     </row>
     <row r="416" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K416" s="5"/>
+      <c r="K416" s="4"/>
     </row>
     <row r="417" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K417" s="5"/>
+      <c r="K417" s="4"/>
     </row>
     <row r="418" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K418" s="5"/>
+      <c r="K418" s="4"/>
     </row>
     <row r="419" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K419" s="5"/>
+      <c r="K419" s="4"/>
     </row>
     <row r="420" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K420" s="5"/>
+      <c r="K420" s="4"/>
     </row>
     <row r="421" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K421" s="5"/>
+      <c r="K421" s="4"/>
     </row>
     <row r="422" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K422" s="5"/>
+      <c r="K422" s="4"/>
     </row>
     <row r="423" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K423" s="5"/>
+      <c r="K423" s="4"/>
     </row>
     <row r="424" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K424" s="5"/>
+      <c r="K424" s="4"/>
     </row>
     <row r="425" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K425" s="5"/>
+      <c r="K425" s="4"/>
     </row>
     <row r="426" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K426" s="5"/>
+      <c r="K426" s="4"/>
     </row>
     <row r="427" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K427" s="5"/>
+      <c r="K427" s="4"/>
     </row>
     <row r="428" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K428" s="5"/>
+      <c r="K428" s="4"/>
     </row>
     <row r="429" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K429" s="5"/>
+      <c r="K429" s="4"/>
     </row>
     <row r="430" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K430" s="5"/>
+      <c r="K430" s="4"/>
     </row>
     <row r="431" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K431" s="5"/>
+      <c r="K431" s="4"/>
     </row>
     <row r="432" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K432" s="5"/>
+      <c r="K432" s="4"/>
     </row>
     <row r="433" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K433" s="5"/>
+      <c r="K433" s="4"/>
     </row>
     <row r="434" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K434" s="5"/>
+      <c r="K434" s="4"/>
     </row>
     <row r="435" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K435" s="5"/>
+      <c r="K435" s="4"/>
     </row>
     <row r="436" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K436" s="5"/>
+      <c r="K436" s="4"/>
     </row>
     <row r="437" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K437" s="5"/>
+      <c r="K437" s="4"/>
     </row>
     <row r="438" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K438" s="5"/>
+      <c r="K438" s="4"/>
     </row>
     <row r="439" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K439" s="5"/>
+      <c r="K439" s="4"/>
     </row>
     <row r="440" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K440" s="5"/>
+      <c r="K440" s="4"/>
     </row>
     <row r="441" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K441" s="5"/>
+      <c r="K441" s="4"/>
     </row>
     <row r="442" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K442" s="5"/>
+      <c r="K442" s="4"/>
     </row>
     <row r="443" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K443" s="5"/>
+      <c r="K443" s="4"/>
     </row>
     <row r="444" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K444" s="5"/>
+      <c r="K444" s="4"/>
     </row>
     <row r="445" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K445" s="5"/>
+      <c r="K445" s="4"/>
     </row>
     <row r="446" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K446" s="5"/>
+      <c r="K446" s="4"/>
     </row>
     <row r="447" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K447" s="5"/>
+      <c r="K447" s="4"/>
     </row>
     <row r="448" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K448" s="5"/>
+      <c r="K448" s="4"/>
     </row>
     <row r="449" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K449" s="5"/>
+      <c r="K449" s="4"/>
     </row>
     <row r="450" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K450" s="5"/>
+      <c r="K450" s="4"/>
     </row>
     <row r="451" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K451" s="5"/>
+      <c r="K451" s="4"/>
     </row>
     <row r="452" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K452" s="5"/>
+      <c r="K452" s="4"/>
     </row>
     <row r="453" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K453" s="5"/>
+      <c r="K453" s="4"/>
     </row>
     <row r="454" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K454" s="5"/>
+      <c r="K454" s="4"/>
     </row>
     <row r="455" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K455" s="5"/>
+      <c r="K455" s="4"/>
     </row>
     <row r="456" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K456" s="5"/>
+      <c r="K456" s="4"/>
     </row>
     <row r="457" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K457" s="5"/>
+      <c r="K457" s="4"/>
     </row>
     <row r="458" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K458" s="5"/>
+      <c r="K458" s="4"/>
     </row>
     <row r="459" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K459" s="5"/>
+      <c r="K459" s="4"/>
     </row>
     <row r="460" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K460" s="5"/>
+      <c r="K460" s="4"/>
     </row>
     <row r="461" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K461" s="5"/>
+      <c r="K461" s="4"/>
     </row>
     <row r="462" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K462" s="5"/>
+      <c r="K462" s="4"/>
     </row>
     <row r="463" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K463" s="5"/>
+      <c r="K463" s="4"/>
     </row>
     <row r="464" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K464" s="5"/>
+      <c r="K464" s="4"/>
     </row>
     <row r="465" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K465" s="5"/>
+      <c r="K465" s="4"/>
     </row>
     <row r="466" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K466" s="5"/>
+      <c r="K466" s="4"/>
     </row>
     <row r="467" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K467" s="5"/>
+      <c r="K467" s="4"/>
     </row>
     <row r="468" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K468" s="5"/>
+      <c r="K468" s="4"/>
     </row>
     <row r="469" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K469" s="5"/>
+      <c r="K469" s="4"/>
     </row>
     <row r="470" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K470" s="5"/>
+      <c r="K470" s="4"/>
     </row>
     <row r="471" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K471" s="5"/>
+      <c r="K471" s="4"/>
     </row>
     <row r="472" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K472" s="5"/>
+      <c r="K472" s="4"/>
     </row>
     <row r="473" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K473" s="5"/>
+      <c r="K473" s="4"/>
     </row>
     <row r="474" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K474" s="5"/>
+      <c r="K474" s="4"/>
     </row>
     <row r="475" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K475" s="5"/>
+      <c r="K475" s="4"/>
     </row>
     <row r="476" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K476" s="5"/>
+      <c r="K476" s="4"/>
     </row>
     <row r="477" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K477" s="5"/>
+      <c r="K477" s="4"/>
     </row>
     <row r="478" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K478" s="5"/>
+      <c r="K478" s="4"/>
     </row>
     <row r="479" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K479" s="5"/>
+      <c r="K479" s="4"/>
     </row>
     <row r="480" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K480" s="5"/>
+      <c r="K480" s="4"/>
     </row>
     <row r="481" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K481" s="5"/>
+      <c r="K481" s="4"/>
     </row>
     <row r="482" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K482" s="5"/>
+      <c r="K482" s="4"/>
     </row>
     <row r="483" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K483" s="5"/>
+      <c r="K483" s="4"/>
     </row>
     <row r="484" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K484" s="5"/>
+      <c r="K484" s="4"/>
     </row>
     <row r="485" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K485" s="5"/>
+      <c r="K485" s="4"/>
     </row>
     <row r="486" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K486" s="5"/>
+      <c r="K486" s="4"/>
     </row>
     <row r="487" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K487" s="5"/>
+      <c r="K487" s="4"/>
     </row>
     <row r="488" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K488" s="5"/>
+      <c r="K488" s="4"/>
     </row>
     <row r="489" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K489" s="5"/>
+      <c r="K489" s="4"/>
     </row>
     <row r="490" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K490" s="5"/>
+      <c r="K490" s="4"/>
     </row>
     <row r="491" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K491" s="5"/>
+      <c r="K491" s="4"/>
     </row>
     <row r="492" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K492" s="5"/>
+      <c r="K492" s="4"/>
     </row>
     <row r="493" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K493" s="5"/>
+      <c r="K493" s="4"/>
     </row>
     <row r="494" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K494" s="5"/>
+      <c r="K494" s="4"/>
     </row>
     <row r="495" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K495" s="5"/>
+      <c r="K495" s="4"/>
     </row>
     <row r="496" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K496" s="5"/>
+      <c r="K496" s="4"/>
     </row>
     <row r="497" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K497" s="5"/>
+      <c r="K497" s="4"/>
     </row>
     <row r="498" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K498" s="5"/>
+      <c r="K498" s="4"/>
     </row>
     <row r="499" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K499" s="5"/>
+      <c r="K499" s="4"/>
     </row>
     <row r="500" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K500" s="5"/>
+      <c r="K500" s="4"/>
     </row>
     <row r="501" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K501" s="5"/>
+      <c r="K501" s="4"/>
     </row>
     <row r="502" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K502" s="5"/>
+      <c r="K502" s="4"/>
     </row>
     <row r="503" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K503" s="5"/>
+      <c r="K503" s="4"/>
     </row>
     <row r="504" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K504" s="5"/>
+      <c r="K504" s="4"/>
     </row>
     <row r="505" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K505" s="5"/>
+      <c r="K505" s="4"/>
     </row>
     <row r="506" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K506" s="5"/>
+      <c r="K506" s="4"/>
     </row>
     <row r="507" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K507" s="5"/>
+      <c r="K507" s="4"/>
     </row>
     <row r="508" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K508" s="5"/>
+      <c r="K508" s="4"/>
     </row>
     <row r="509" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K509" s="5"/>
+      <c r="K509" s="4"/>
     </row>
     <row r="510" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K510" s="5"/>
+      <c r="K510" s="4"/>
     </row>
     <row r="511" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K511" s="5"/>
+      <c r="K511" s="4"/>
     </row>
     <row r="512" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K512" s="5"/>
+      <c r="K512" s="4"/>
     </row>
     <row r="513" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K513" s="5"/>
+      <c r="K513" s="4"/>
     </row>
     <row r="514" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K514" s="5"/>
+      <c r="K514" s="4"/>
     </row>
     <row r="515" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K515" s="5"/>
+      <c r="K515" s="4"/>
     </row>
     <row r="516" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K516" s="5"/>
+      <c r="K516" s="4"/>
     </row>
     <row r="517" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K517" s="5"/>
+      <c r="K517" s="4"/>
     </row>
     <row r="518" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K518" s="5"/>
+      <c r="K518" s="4"/>
     </row>
     <row r="519" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K519" s="5"/>
+      <c r="K519" s="4"/>
     </row>
     <row r="520" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K520" s="5"/>
+      <c r="K520" s="4"/>
     </row>
     <row r="521" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K521" s="5"/>
+      <c r="K521" s="4"/>
     </row>
     <row r="522" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K522" s="5"/>
+      <c r="K522" s="4"/>
     </row>
     <row r="523" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K523" s="5"/>
+      <c r="K523" s="4"/>
     </row>
     <row r="524" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K524" s="5"/>
+      <c r="K524" s="4"/>
     </row>
     <row r="525" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K525" s="5"/>
+      <c r="K525" s="4"/>
     </row>
     <row r="526" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K526" s="5"/>
+      <c r="K526" s="4"/>
     </row>
     <row r="527" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K527" s="5"/>
+      <c r="K527" s="4"/>
     </row>
     <row r="528" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K528" s="5"/>
+      <c r="K528" s="4"/>
     </row>
     <row r="529" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K529" s="5"/>
+      <c r="K529" s="4"/>
     </row>
     <row r="530" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K530" s="5"/>
+      <c r="K530" s="4"/>
     </row>
     <row r="531" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K531" s="5"/>
+      <c r="K531" s="4"/>
     </row>
     <row r="532" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K532" s="5"/>
+      <c r="K532" s="4"/>
     </row>
     <row r="533" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K533" s="5"/>
+      <c r="K533" s="4"/>
     </row>
     <row r="534" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K534" s="5"/>
+      <c r="K534" s="4"/>
     </row>
     <row r="535" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K535" s="5"/>
+      <c r="K535" s="4"/>
     </row>
     <row r="536" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K536" s="5"/>
+      <c r="K536" s="4"/>
     </row>
     <row r="537" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K537" s="5"/>
+      <c r="K537" s="4"/>
     </row>
     <row r="538" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K538" s="5"/>
+      <c r="K538" s="4"/>
     </row>
     <row r="539" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K539" s="5"/>
+      <c r="K539" s="4"/>
     </row>
     <row r="540" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K540" s="5"/>
+      <c r="K540" s="4"/>
     </row>
     <row r="541" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K541" s="5"/>
+      <c r="K541" s="4"/>
     </row>
     <row r="542" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K542" s="5"/>
+      <c r="K542" s="4"/>
     </row>
     <row r="543" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K543" s="5"/>
+      <c r="K543" s="4"/>
     </row>
     <row r="544" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K544" s="5"/>
+      <c r="K544" s="4"/>
     </row>
     <row r="545" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K545" s="5"/>
+      <c r="K545" s="4"/>
     </row>
     <row r="546" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K546" s="5"/>
+      <c r="K546" s="4"/>
     </row>
     <row r="547" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K547" s="5"/>
+      <c r="K547" s="4"/>
     </row>
     <row r="548" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K548" s="5"/>
+      <c r="K548" s="4"/>
     </row>
     <row r="549" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K549" s="5"/>
+      <c r="K549" s="4"/>
     </row>
     <row r="550" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K550" s="5"/>
+      <c r="K550" s="4"/>
     </row>
     <row r="551" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K551" s="5"/>
+      <c r="K551" s="4"/>
     </row>
     <row r="552" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K552" s="5"/>
+      <c r="K552" s="4"/>
     </row>
     <row r="553" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K553" s="5"/>
+      <c r="K553" s="4"/>
     </row>
     <row r="554" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K554" s="5"/>
+      <c r="K554" s="4"/>
     </row>
     <row r="555" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K555" s="5"/>
+      <c r="K555" s="4"/>
     </row>
     <row r="556" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K556" s="5"/>
+      <c r="K556" s="4"/>
     </row>
     <row r="557" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K557" s="5"/>
+      <c r="K557" s="4"/>
     </row>
     <row r="558" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K558" s="5"/>
+      <c r="K558" s="4"/>
     </row>
     <row r="559" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K559" s="5"/>
+      <c r="K559" s="4"/>
     </row>
     <row r="560" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K560" s="5"/>
+      <c r="K560" s="4"/>
     </row>
     <row r="561" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K561" s="5"/>
+      <c r="K561" s="4"/>
     </row>
     <row r="562" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K562" s="5"/>
+      <c r="K562" s="4"/>
     </row>
     <row r="563" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K563" s="5"/>
+      <c r="K563" s="4"/>
     </row>
     <row r="564" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K564" s="5"/>
+      <c r="K564" s="4"/>
     </row>
     <row r="565" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K565" s="5"/>
+      <c r="K565" s="4"/>
     </row>
     <row r="566" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K566" s="5"/>
+      <c r="K566" s="4"/>
     </row>
     <row r="567" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K567" s="5"/>
+      <c r="K567" s="4"/>
     </row>
     <row r="568" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K568" s="5"/>
+      <c r="K568" s="4"/>
     </row>
     <row r="569" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K569" s="5"/>
+      <c r="K569" s="4"/>
     </row>
     <row r="570" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K570" s="5"/>
+      <c r="K570" s="4"/>
     </row>
     <row r="571" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K571" s="5"/>
+      <c r="K571" s="4"/>
     </row>
     <row r="572" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K572" s="5"/>
+      <c r="K572" s="4"/>
     </row>
     <row r="573" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K573" s="5"/>
+      <c r="K573" s="4"/>
     </row>
     <row r="574" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K574" s="5"/>
+      <c r="K574" s="4"/>
     </row>
     <row r="575" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K575" s="5"/>
+      <c r="K575" s="4"/>
     </row>
     <row r="576" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K576" s="5"/>
+      <c r="K576" s="4"/>
     </row>
     <row r="577" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K577" s="5"/>
+      <c r="K577" s="4"/>
     </row>
     <row r="578" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K578" s="5"/>
+      <c r="K578" s="4"/>
     </row>
     <row r="579" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K579" s="5"/>
+      <c r="K579" s="4"/>
     </row>
     <row r="580" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K580" s="5"/>
+      <c r="K580" s="4"/>
     </row>
     <row r="581" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K581" s="5"/>
+      <c r="K581" s="4"/>
     </row>
     <row r="582" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K582" s="5"/>
+      <c r="K582" s="4"/>
     </row>
     <row r="583" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K583" s="5"/>
+      <c r="K583" s="4"/>
     </row>
     <row r="584" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K584" s="5"/>
+      <c r="K584" s="4"/>
     </row>
     <row r="585" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K585" s="5"/>
+      <c r="K585" s="4"/>
     </row>
     <row r="586" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K586" s="5"/>
+      <c r="K586" s="4"/>
     </row>
     <row r="587" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K587" s="5"/>
+      <c r="K587" s="4"/>
     </row>
     <row r="588" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K588" s="5"/>
+      <c r="K588" s="4"/>
     </row>
     <row r="589" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K589" s="5"/>
+      <c r="K589" s="4"/>
     </row>
     <row r="590" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K590" s="5"/>
+      <c r="K590" s="4"/>
     </row>
     <row r="591" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K591" s="5"/>
+      <c r="K591" s="4"/>
     </row>
     <row r="592" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K592" s="5"/>
+      <c r="K592" s="4"/>
     </row>
     <row r="593" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K593" s="5"/>
+      <c r="K593" s="4"/>
     </row>
     <row r="594" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K594" s="5"/>
+      <c r="K594" s="4"/>
     </row>
     <row r="595" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K595" s="5"/>
+      <c r="K595" s="4"/>
     </row>
     <row r="596" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K596" s="5"/>
+      <c r="K596" s="4"/>
     </row>
     <row r="597" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K597" s="5"/>
+      <c r="K597" s="4"/>
     </row>
     <row r="598" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K598" s="5"/>
+      <c r="K598" s="4"/>
     </row>
     <row r="599" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K599" s="5"/>
+      <c r="K599" s="4"/>
     </row>
     <row r="600" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K600" s="5"/>
+      <c r="K600" s="4"/>
     </row>
     <row r="601" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K601" s="5"/>
+      <c r="K601" s="4"/>
     </row>
     <row r="602" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K602" s="5"/>
+      <c r="K602" s="4"/>
     </row>
     <row r="603" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K603" s="5"/>
+      <c r="K603" s="4"/>
     </row>
     <row r="604" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K604" s="5"/>
+      <c r="K604" s="4"/>
     </row>
     <row r="605" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K605" s="5"/>
+      <c r="K605" s="4"/>
     </row>
     <row r="606" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K606" s="5"/>
+      <c r="K606" s="4"/>
     </row>
     <row r="607" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K607" s="5"/>
+      <c r="K607" s="4"/>
     </row>
     <row r="608" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K608" s="5"/>
+      <c r="K608" s="4"/>
     </row>
     <row r="609" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K609" s="5"/>
+      <c r="K609" s="4"/>
     </row>
     <row r="610" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K610" s="5"/>
+      <c r="K610" s="4"/>
     </row>
     <row r="611" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K611" s="5"/>
+      <c r="K611" s="4"/>
     </row>
     <row r="612" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K612" s="5"/>
+      <c r="K612" s="4"/>
     </row>
     <row r="613" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K613" s="5"/>
+      <c r="K613" s="4"/>
     </row>
     <row r="614" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K614" s="5"/>
+      <c r="K614" s="4"/>
     </row>
     <row r="615" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K615" s="5"/>
+      <c r="K615" s="4"/>
     </row>
     <row r="616" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K616" s="5"/>
+      <c r="K616" s="4"/>
     </row>
     <row r="617" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K617" s="5"/>
+      <c r="K617" s="4"/>
     </row>
     <row r="618" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K618" s="5"/>
+      <c r="K618" s="4"/>
     </row>
     <row r="619" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K619" s="5"/>
+      <c r="K619" s="4"/>
     </row>
     <row r="620" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K620" s="5"/>
+      <c r="K620" s="4"/>
     </row>
     <row r="621" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K621" s="5"/>
+      <c r="K621" s="4"/>
     </row>
     <row r="622" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K622" s="5"/>
+      <c r="K622" s="4"/>
     </row>
     <row r="623" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K623" s="5"/>
+      <c r="K623" s="4"/>
     </row>
     <row r="624" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K624" s="5"/>
+      <c r="K624" s="4"/>
     </row>
     <row r="625" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K625" s="5"/>
+      <c r="K625" s="4"/>
     </row>
     <row r="626" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K626" s="5"/>
+      <c r="K626" s="4"/>
     </row>
     <row r="627" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K627" s="5"/>
+      <c r="K627" s="4"/>
     </row>
     <row r="628" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K628" s="5"/>
+      <c r="K628" s="4"/>
     </row>
     <row r="629" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K629" s="5"/>
+      <c r="K629" s="4"/>
     </row>
     <row r="630" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K630" s="5"/>
+      <c r="K630" s="4"/>
     </row>
     <row r="631" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K631" s="5"/>
+      <c r="K631" s="4"/>
     </row>
     <row r="632" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K632" s="5"/>
+      <c r="K632" s="4"/>
     </row>
     <row r="633" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K633" s="5"/>
+      <c r="K633" s="4"/>
     </row>
     <row r="634" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K634" s="5"/>
+      <c r="K634" s="4"/>
     </row>
     <row r="635" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K635" s="5"/>
+      <c r="K635" s="4"/>
     </row>
     <row r="636" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K636" s="5"/>
+      <c r="K636" s="4"/>
     </row>
     <row r="637" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K637" s="5"/>
+      <c r="K637" s="4"/>
     </row>
     <row r="638" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K638" s="5"/>
+      <c r="K638" s="4"/>
     </row>
     <row r="639" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K639" s="5"/>
+      <c r="K639" s="4"/>
     </row>
     <row r="640" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K640" s="5"/>
+      <c r="K640" s="4"/>
     </row>
     <row r="641" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K641" s="5"/>
+      <c r="K641" s="4"/>
     </row>
     <row r="642" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K642" s="5"/>
+      <c r="K642" s="4"/>
     </row>
     <row r="643" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K643" s="5"/>
+      <c r="K643" s="4"/>
     </row>
     <row r="644" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K644" s="5"/>
+      <c r="K644" s="4"/>
     </row>
     <row r="645" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K645" s="5"/>
+      <c r="K645" s="4"/>
     </row>
     <row r="646" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K646" s="5"/>
+      <c r="K646" s="4"/>
     </row>
     <row r="647" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K647" s="5"/>
+      <c r="K647" s="4"/>
     </row>
     <row r="648" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K648" s="5"/>
+      <c r="K648" s="4"/>
     </row>
     <row r="649" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K649" s="5"/>
+      <c r="K649" s="4"/>
     </row>
     <row r="650" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K650" s="5"/>
+      <c r="K650" s="4"/>
     </row>
     <row r="651" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K651" s="5"/>
+      <c r="K651" s="4"/>
     </row>
     <row r="652" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K652" s="5"/>
+      <c r="K652" s="4"/>
     </row>
     <row r="653" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K653" s="5"/>
+      <c r="K653" s="4"/>
     </row>
     <row r="654" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K654" s="5"/>
+      <c r="K654" s="4"/>
     </row>
     <row r="655" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K655" s="5"/>
+      <c r="K655" s="4"/>
     </row>
     <row r="656" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K656" s="5"/>
+      <c r="K656" s="4"/>
     </row>
     <row r="657" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K657" s="5"/>
+      <c r="K657" s="4"/>
     </row>
     <row r="658" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K658" s="5"/>
+      <c r="K658" s="4"/>
     </row>
     <row r="659" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K659" s="5"/>
+      <c r="K659" s="4"/>
     </row>
     <row r="660" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K660" s="5"/>
+      <c r="K660" s="4"/>
     </row>
     <row r="661" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K661" s="5"/>
+      <c r="K661" s="4"/>
     </row>
     <row r="662" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K662" s="5"/>
+      <c r="K662" s="4"/>
     </row>
     <row r="663" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K663" s="5"/>
+      <c r="K663" s="4"/>
     </row>
     <row r="664" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K664" s="5"/>
+      <c r="K664" s="4"/>
     </row>
     <row r="665" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K665" s="5"/>
+      <c r="K665" s="4"/>
     </row>
     <row r="666" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K666" s="5"/>
+      <c r="K666" s="4"/>
     </row>
     <row r="667" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K667" s="5"/>
+      <c r="K667" s="4"/>
     </row>
     <row r="668" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K668" s="5"/>
+      <c r="K668" s="4"/>
     </row>
     <row r="669" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K669" s="5"/>
+      <c r="K669" s="4"/>
     </row>
     <row r="670" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K670" s="5"/>
+      <c r="K670" s="4"/>
     </row>
     <row r="671" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K671" s="5"/>
+      <c r="K671" s="4"/>
     </row>
     <row r="672" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K672" s="5"/>
+      <c r="K672" s="4"/>
     </row>
     <row r="673" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K673" s="5"/>
+      <c r="K673" s="4"/>
     </row>
     <row r="674" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K674" s="5"/>
+      <c r="K674" s="4"/>
     </row>
     <row r="675" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K675" s="5"/>
+      <c r="K675" s="4"/>
     </row>
     <row r="676" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K676" s="5"/>
+      <c r="K676" s="4"/>
     </row>
     <row r="677" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K677" s="5"/>
+      <c r="K677" s="4"/>
     </row>
     <row r="678" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K678" s="5"/>
+      <c r="K678" s="4"/>
     </row>
     <row r="679" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K679" s="5"/>
+      <c r="K679" s="4"/>
     </row>
     <row r="680" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K680" s="5"/>
+      <c r="K680" s="4"/>
     </row>
     <row r="681" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K681" s="5"/>
+      <c r="K681" s="4"/>
     </row>
     <row r="682" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K682" s="5"/>
+      <c r="K682" s="4"/>
     </row>
     <row r="683" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K683" s="5"/>
+      <c r="K683" s="4"/>
     </row>
     <row r="684" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K684" s="5"/>
+      <c r="K684" s="4"/>
     </row>
     <row r="685" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K685" s="5"/>
+      <c r="K685" s="4"/>
     </row>
     <row r="686" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K686" s="5"/>
+      <c r="K686" s="4"/>
     </row>
     <row r="687" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K687" s="5"/>
+      <c r="K687" s="4"/>
     </row>
     <row r="688" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K688" s="5"/>
+      <c r="K688" s="4"/>
     </row>
     <row r="689" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K689" s="5"/>
+      <c r="K689" s="4"/>
     </row>
     <row r="690" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K690" s="5"/>
+      <c r="K690" s="4"/>
     </row>
     <row r="691" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K691" s="5"/>
+      <c r="K691" s="4"/>
     </row>
     <row r="692" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K692" s="5"/>
+      <c r="K692" s="4"/>
     </row>
     <row r="693" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K693" s="5"/>
+      <c r="K693" s="4"/>
     </row>
     <row r="694" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K694" s="5"/>
+      <c r="K694" s="4"/>
     </row>
     <row r="695" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K695" s="5"/>
+      <c r="K695" s="4"/>
     </row>
     <row r="696" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K696" s="5"/>
+      <c r="K696" s="4"/>
     </row>
     <row r="697" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K697" s="5"/>
+      <c r="K697" s="4"/>
     </row>
     <row r="698" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K698" s="5"/>
+      <c r="K698" s="4"/>
     </row>
     <row r="699" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K699" s="5"/>
+      <c r="K699" s="4"/>
     </row>
     <row r="700" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K700" s="5"/>
+      <c r="K700" s="4"/>
     </row>
     <row r="701" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K701" s="5"/>
+      <c r="K701" s="4"/>
     </row>
     <row r="702" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K702" s="5"/>
+      <c r="K702" s="4"/>
     </row>
     <row r="703" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K703" s="5"/>
+      <c r="K703" s="4"/>
     </row>
     <row r="704" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K704" s="5"/>
+      <c r="K704" s="4"/>
     </row>
     <row r="705" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K705" s="5"/>
+      <c r="K705" s="4"/>
     </row>
     <row r="706" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K706" s="5"/>
+      <c r="K706" s="4"/>
     </row>
     <row r="707" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K707" s="5"/>
+      <c r="K707" s="4"/>
     </row>
     <row r="708" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K708" s="5"/>
+      <c r="K708" s="4"/>
     </row>
     <row r="709" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K709" s="5"/>
+      <c r="K709" s="4"/>
     </row>
     <row r="710" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K710" s="5"/>
+      <c r="K710" s="4"/>
     </row>
     <row r="711" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K711" s="5"/>
+      <c r="K711" s="4"/>
     </row>
     <row r="712" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K712" s="5"/>
+      <c r="K712" s="4"/>
     </row>
     <row r="713" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K713" s="5"/>
+      <c r="K713" s="4"/>
     </row>
     <row r="714" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K714" s="5"/>
+      <c r="K714" s="4"/>
     </row>
     <row r="715" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K715" s="5"/>
+      <c r="K715" s="4"/>
     </row>
     <row r="716" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K716" s="5"/>
+      <c r="K716" s="4"/>
     </row>
     <row r="717" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K717" s="5"/>
+      <c r="K717" s="4"/>
     </row>
     <row r="718" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K718" s="5"/>
+      <c r="K718" s="4"/>
     </row>
     <row r="719" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K719" s="5"/>
+      <c r="K719" s="4"/>
     </row>
     <row r="720" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K720" s="5"/>
+      <c r="K720" s="4"/>
     </row>
     <row r="721" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K721" s="5"/>
+      <c r="K721" s="4"/>
     </row>
     <row r="722" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K722" s="5"/>
+      <c r="K722" s="4"/>
     </row>
     <row r="723" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K723" s="5"/>
+      <c r="K723" s="4"/>
     </row>
     <row r="724" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K724" s="5"/>
+      <c r="K724" s="4"/>
     </row>
     <row r="725" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K725" s="5"/>
+      <c r="K725" s="4"/>
     </row>
     <row r="726" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K726" s="5"/>
+      <c r="K726" s="4"/>
     </row>
     <row r="727" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K727" s="5"/>
+      <c r="K727" s="4"/>
     </row>
     <row r="728" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K728" s="5"/>
+      <c r="K728" s="4"/>
     </row>
     <row r="729" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K729" s="5"/>
+      <c r="K729" s="4"/>
     </row>
     <row r="730" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K730" s="5"/>
+      <c r="K730" s="4"/>
     </row>
     <row r="731" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K731" s="5"/>
+      <c r="K731" s="4"/>
     </row>
     <row r="732" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K732" s="5"/>
+      <c r="K732" s="4"/>
     </row>
     <row r="733" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K733" s="5"/>
+      <c r="K733" s="4"/>
     </row>
     <row r="734" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K734" s="5"/>
+      <c r="K734" s="4"/>
     </row>
     <row r="735" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K735" s="5"/>
+      <c r="K735" s="4"/>
     </row>
     <row r="736" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K736" s="5"/>
+      <c r="K736" s="4"/>
     </row>
     <row r="737" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K737" s="5"/>
+      <c r="K737" s="4"/>
     </row>
     <row r="738" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K738" s="5"/>
+      <c r="K738" s="4"/>
     </row>
     <row r="739" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K739" s="5"/>
+      <c r="K739" s="4"/>
     </row>
     <row r="740" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K740" s="5"/>
+      <c r="K740" s="4"/>
     </row>
     <row r="741" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K741" s="5"/>
+      <c r="K741" s="4"/>
     </row>
     <row r="742" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K742" s="5"/>
+      <c r="K742" s="4"/>
     </row>
     <row r="743" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K743" s="5"/>
+      <c r="K743" s="4"/>
     </row>
     <row r="744" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K744" s="5"/>
+      <c r="K744" s="4"/>
     </row>
     <row r="745" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K745" s="5"/>
+      <c r="K745" s="4"/>
     </row>
     <row r="746" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K746" s="5"/>
+      <c r="K746" s="4"/>
     </row>
     <row r="747" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K747" s="5"/>
+      <c r="K747" s="4"/>
     </row>
     <row r="748" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K748" s="5"/>
+      <c r="K748" s="4"/>
     </row>
     <row r="749" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K749" s="5"/>
+      <c r="K749" s="4"/>
     </row>
     <row r="750" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K750" s="5"/>
+      <c r="K750" s="4"/>
     </row>
     <row r="751" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K751" s="5"/>
+      <c r="K751" s="4"/>
     </row>
     <row r="752" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K752" s="5"/>
+      <c r="K752" s="4"/>
     </row>
     <row r="753" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K753" s="5"/>
+      <c r="K753" s="4"/>
     </row>
     <row r="754" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K754" s="5"/>
+      <c r="K754" s="4"/>
     </row>
     <row r="755" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K755" s="5"/>
+      <c r="K755" s="4"/>
     </row>
     <row r="756" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K756" s="5"/>
+      <c r="K756" s="4"/>
     </row>
     <row r="757" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K757" s="5"/>
+      <c r="K757" s="4"/>
     </row>
     <row r="758" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K758" s="5"/>
+      <c r="K758" s="4"/>
     </row>
     <row r="759" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K759" s="5"/>
+      <c r="K759" s="4"/>
     </row>
     <row r="760" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K760" s="5"/>
+      <c r="K760" s="4"/>
     </row>
     <row r="761" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K761" s="5"/>
+      <c r="K761" s="4"/>
     </row>
     <row r="762" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K762" s="5"/>
+      <c r="K762" s="4"/>
     </row>
     <row r="763" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K763" s="5"/>
+      <c r="K763" s="4"/>
     </row>
     <row r="764" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K764" s="5"/>
+      <c r="K764" s="4"/>
     </row>
     <row r="765" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K765" s="5"/>
+      <c r="K765" s="4"/>
     </row>
     <row r="766" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K766" s="5"/>
+      <c r="K766" s="4"/>
     </row>
     <row r="767" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K767" s="5"/>
+      <c r="K767" s="4"/>
     </row>
     <row r="768" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K768" s="5"/>
+      <c r="K768" s="4"/>
     </row>
     <row r="769" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K769" s="5"/>
+      <c r="K769" s="4"/>
     </row>
     <row r="770" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K770" s="5"/>
+      <c r="K770" s="4"/>
     </row>
     <row r="771" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K771" s="5"/>
+      <c r="K771" s="4"/>
     </row>
     <row r="772" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K772" s="5"/>
+      <c r="K772" s="4"/>
     </row>
     <row r="773" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K773" s="5"/>
+      <c r="K773" s="4"/>
     </row>
     <row r="774" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K774" s="5"/>
+      <c r="K774" s="4"/>
     </row>
     <row r="775" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K775" s="5"/>
+      <c r="K775" s="4"/>
     </row>
     <row r="776" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K776" s="5"/>
+      <c r="K776" s="4"/>
     </row>
     <row r="777" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K777" s="5"/>
+      <c r="K777" s="4"/>
     </row>
     <row r="778" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K778" s="5"/>
+      <c r="K778" s="4"/>
     </row>
     <row r="779" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K779" s="5"/>
+      <c r="K779" s="4"/>
     </row>
     <row r="780" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K780" s="5"/>
+      <c r="K780" s="4"/>
     </row>
     <row r="781" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K781" s="5"/>
+      <c r="K781" s="4"/>
     </row>
     <row r="782" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K782" s="5"/>
+      <c r="K782" s="4"/>
     </row>
     <row r="783" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K783" s="5"/>
+      <c r="K783" s="4"/>
     </row>
     <row r="784" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K784" s="5"/>
+      <c r="K784" s="4"/>
     </row>
     <row r="785" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K785" s="5"/>
+      <c r="K785" s="4"/>
     </row>
     <row r="786" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K786" s="5"/>
+      <c r="K786" s="4"/>
     </row>
     <row r="787" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K787" s="5"/>
+      <c r="K787" s="4"/>
     </row>
     <row r="788" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K788" s="5"/>
+      <c r="K788" s="4"/>
     </row>
     <row r="789" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K789" s="5"/>
+      <c r="K789" s="4"/>
     </row>
     <row r="790" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K790" s="5"/>
+      <c r="K790" s="4"/>
     </row>
     <row r="791" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K791" s="5"/>
+      <c r="K791" s="4"/>
     </row>
     <row r="792" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K792" s="5"/>
+      <c r="K792" s="4"/>
     </row>
     <row r="793" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K793" s="5"/>
+      <c r="K793" s="4"/>
     </row>
     <row r="794" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K794" s="5"/>
+      <c r="K794" s="4"/>
     </row>
     <row r="795" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K795" s="5"/>
+      <c r="K795" s="4"/>
     </row>
     <row r="796" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K796" s="5"/>
+      <c r="K796" s="4"/>
     </row>
     <row r="797" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K797" s="5"/>
+      <c r="K797" s="4"/>
     </row>
     <row r="798" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K798" s="5"/>
+      <c r="K798" s="4"/>
     </row>
     <row r="799" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K799" s="5"/>
+      <c r="K799" s="4"/>
     </row>
     <row r="800" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K800" s="5"/>
+      <c r="K800" s="4"/>
     </row>
     <row r="801" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K801" s="5"/>
+      <c r="K801" s="4"/>
     </row>
     <row r="802" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K802" s="5"/>
+      <c r="K802" s="4"/>
     </row>
     <row r="803" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K803" s="5"/>
+      <c r="K803" s="4"/>
     </row>
     <row r="804" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K804" s="5"/>
+      <c r="K804" s="4"/>
     </row>
     <row r="805" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K805" s="5"/>
+      <c r="K805" s="4"/>
     </row>
     <row r="806" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K806" s="5"/>
+      <c r="K806" s="4"/>
     </row>
     <row r="807" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K807" s="5"/>
+      <c r="K807" s="4"/>
     </row>
     <row r="808" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K808" s="5"/>
+      <c r="K808" s="4"/>
     </row>
     <row r="809" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K809" s="5"/>
+      <c r="K809" s="4"/>
     </row>
     <row r="810" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K810" s="5"/>
+      <c r="K810" s="4"/>
     </row>
     <row r="811" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K811" s="5"/>
+      <c r="K811" s="4"/>
     </row>
     <row r="812" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K812" s="5"/>
+      <c r="K812" s="4"/>
     </row>
     <row r="813" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K813" s="5"/>
+      <c r="K813" s="4"/>
     </row>
     <row r="814" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K814" s="5"/>
+      <c r="K814" s="4"/>
     </row>
     <row r="815" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K815" s="5"/>
+      <c r="K815" s="4"/>
     </row>
     <row r="816" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K816" s="5"/>
+      <c r="K816" s="4"/>
     </row>
     <row r="817" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K817" s="5"/>
+      <c r="K817" s="4"/>
     </row>
     <row r="818" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K818" s="5"/>
+      <c r="K818" s="4"/>
     </row>
     <row r="819" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K819" s="5"/>
+      <c r="K819" s="4"/>
     </row>
     <row r="820" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K820" s="5"/>
+      <c r="K820" s="4"/>
     </row>
     <row r="821" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K821" s="5"/>
+      <c r="K821" s="4"/>
     </row>
     <row r="822" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K822" s="5"/>
+      <c r="K822" s="4"/>
     </row>
     <row r="823" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K823" s="5"/>
+      <c r="K823" s="4"/>
     </row>
     <row r="824" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K824" s="5"/>
+      <c r="K824" s="4"/>
     </row>
     <row r="825" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K825" s="5"/>
+      <c r="K825" s="4"/>
     </row>
     <row r="826" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K826" s="5"/>
+      <c r="K826" s="4"/>
     </row>
     <row r="827" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K827" s="5"/>
+      <c r="K827" s="4"/>
     </row>
     <row r="828" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K828" s="5"/>
+      <c r="K828" s="4"/>
     </row>
     <row r="829" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K829" s="5"/>
+      <c r="K829" s="4"/>
     </row>
     <row r="830" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K830" s="5"/>
+      <c r="K830" s="4"/>
     </row>
     <row r="831" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K831" s="5"/>
+      <c r="K831" s="4"/>
     </row>
     <row r="832" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K832" s="5"/>
+      <c r="K832" s="4"/>
     </row>
     <row r="833" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K833" s="5"/>
+      <c r="K833" s="4"/>
     </row>
     <row r="834" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K834" s="5"/>
+      <c r="K834" s="4"/>
     </row>
     <row r="835" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K835" s="5"/>
+      <c r="K835" s="4"/>
     </row>
     <row r="836" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K836" s="5"/>
+      <c r="K836" s="4"/>
     </row>
     <row r="837" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K837" s="5"/>
+      <c r="K837" s="4"/>
     </row>
     <row r="838" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K838" s="5"/>
+      <c r="K838" s="4"/>
     </row>
     <row r="839" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K839" s="5"/>
+      <c r="K839" s="4"/>
     </row>
     <row r="840" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K840" s="5"/>
+      <c r="K840" s="4"/>
     </row>
     <row r="841" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K841" s="5"/>
+      <c r="K841" s="4"/>
     </row>
     <row r="842" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K842" s="5"/>
+      <c r="K842" s="4"/>
     </row>
     <row r="843" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K843" s="5"/>
+      <c r="K843" s="4"/>
     </row>
     <row r="844" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K844" s="5"/>
+      <c r="K844" s="4"/>
     </row>
     <row r="845" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K845" s="5"/>
+      <c r="K845" s="4"/>
     </row>
     <row r="846" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K846" s="5"/>
+      <c r="K846" s="4"/>
     </row>
     <row r="847" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K847" s="5"/>
+      <c r="K847" s="4"/>
     </row>
     <row r="848" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K848" s="5"/>
+      <c r="K848" s="4"/>
     </row>
     <row r="849" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K849" s="5"/>
+      <c r="K849" s="4"/>
     </row>
     <row r="850" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K850" s="5"/>
+      <c r="K850" s="4"/>
     </row>
     <row r="851" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K851" s="5"/>
+      <c r="K851" s="4"/>
     </row>
     <row r="852" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K852" s="5"/>
+      <c r="K852" s="4"/>
     </row>
     <row r="853" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K853" s="5"/>
+      <c r="K853" s="4"/>
     </row>
     <row r="854" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K854" s="5"/>
+      <c r="K854" s="4"/>
     </row>
     <row r="855" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K855" s="5"/>
+      <c r="K855" s="4"/>
     </row>
     <row r="856" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K856" s="5"/>
+      <c r="K856" s="4"/>
     </row>
     <row r="857" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K857" s="5"/>
+      <c r="K857" s="4"/>
     </row>
     <row r="858" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K858" s="5"/>
+      <c r="K858" s="4"/>
     </row>
     <row r="859" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K859" s="5"/>
+      <c r="K859" s="4"/>
     </row>
     <row r="860" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K860" s="5"/>
+      <c r="K860" s="4"/>
     </row>
     <row r="861" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K861" s="5"/>
+      <c r="K861" s="4"/>
     </row>
     <row r="862" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K862" s="5"/>
+      <c r="K862" s="4"/>
     </row>
     <row r="863" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K863" s="5"/>
+      <c r="K863" s="4"/>
     </row>
     <row r="864" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K864" s="5"/>
+      <c r="K864" s="4"/>
     </row>
     <row r="865" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K865" s="5"/>
+      <c r="K865" s="4"/>
     </row>
     <row r="866" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K866" s="5"/>
+      <c r="K866" s="4"/>
     </row>
     <row r="867" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K867" s="5"/>
+      <c r="K867" s="4"/>
     </row>
     <row r="868" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K868" s="5"/>
+      <c r="K868" s="4"/>
     </row>
     <row r="869" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K869" s="5"/>
+      <c r="K869" s="4"/>
     </row>
     <row r="870" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K870" s="5"/>
+      <c r="K870" s="4"/>
     </row>
     <row r="871" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K871" s="5"/>
+      <c r="K871" s="4"/>
     </row>
     <row r="872" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K872" s="5"/>
+      <c r="K872" s="4"/>
     </row>
     <row r="873" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K873" s="5"/>
+      <c r="K873" s="4"/>
     </row>
     <row r="874" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K874" s="5"/>
+      <c r="K874" s="4"/>
     </row>
     <row r="875" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K875" s="5"/>
+      <c r="K875" s="4"/>
     </row>
     <row r="876" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K876" s="5"/>
+      <c r="K876" s="4"/>
     </row>
     <row r="877" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K877" s="5"/>
+      <c r="K877" s="4"/>
     </row>
     <row r="878" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K878" s="5"/>
+      <c r="K878" s="4"/>
     </row>
     <row r="879" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K879" s="5"/>
+      <c r="K879" s="4"/>
     </row>
     <row r="880" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K880" s="5"/>
+      <c r="K880" s="4"/>
     </row>
     <row r="881" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K881" s="5"/>
+      <c r="K881" s="4"/>
     </row>
     <row r="882" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K882" s="5"/>
+      <c r="K882" s="4"/>
     </row>
     <row r="883" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K883" s="5"/>
+      <c r="K883" s="4"/>
     </row>
     <row r="884" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K884" s="5"/>
+      <c r="K884" s="4"/>
     </row>
     <row r="885" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K885" s="5"/>
+      <c r="K885" s="4"/>
     </row>
     <row r="886" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K886" s="5"/>
+      <c r="K886" s="4"/>
     </row>
     <row r="887" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K887" s="5"/>
+      <c r="K887" s="4"/>
     </row>
     <row r="888" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K888" s="5"/>
+      <c r="K888" s="4"/>
     </row>
     <row r="889" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K889" s="5"/>
+      <c r="K889" s="4"/>
     </row>
     <row r="890" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K890" s="5"/>
+      <c r="K890" s="4"/>
     </row>
     <row r="891" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K891" s="5"/>
+      <c r="K891" s="4"/>
     </row>
     <row r="892" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K892" s="5"/>
+      <c r="K892" s="4"/>
     </row>
     <row r="893" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K893" s="5"/>
+      <c r="K893" s="4"/>
     </row>
     <row r="894" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K894" s="5"/>
+      <c r="K894" s="4"/>
     </row>
     <row r="895" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K895" s="5"/>
+      <c r="K895" s="4"/>
     </row>
     <row r="896" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K896" s="5"/>
+      <c r="K896" s="4"/>
     </row>
     <row r="897" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K897" s="5"/>
+      <c r="K897" s="4"/>
     </row>
     <row r="898" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K898" s="5"/>
+      <c r="K898" s="4"/>
     </row>
     <row r="899" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K899" s="5"/>
+      <c r="K899" s="4"/>
     </row>
     <row r="900" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K900" s="5"/>
+      <c r="K900" s="4"/>
     </row>
     <row r="901" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K901" s="5"/>
+      <c r="K901" s="4"/>
     </row>
     <row r="902" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K902" s="5"/>
+      <c r="K902" s="4"/>
     </row>
     <row r="903" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K903" s="5"/>
+      <c r="K903" s="4"/>
     </row>
     <row r="904" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K904" s="5"/>
+      <c r="K904" s="4"/>
     </row>
     <row r="905" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K905" s="5"/>
+      <c r="K905" s="4"/>
     </row>
     <row r="906" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K906" s="5"/>
+      <c r="K906" s="4"/>
     </row>
     <row r="907" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K907" s="5"/>
+      <c r="K907" s="4"/>
     </row>
     <row r="908" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K908" s="5"/>
+      <c r="K908" s="4"/>
     </row>
     <row r="909" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K909" s="5"/>
+      <c r="K909" s="4"/>
     </row>
     <row r="910" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K910" s="5"/>
+      <c r="K910" s="4"/>
     </row>
     <row r="911" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K911" s="5"/>
+      <c r="K911" s="4"/>
     </row>
     <row r="912" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K912" s="5"/>
+      <c r="K912" s="4"/>
     </row>
     <row r="913" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K913" s="5"/>
+      <c r="K913" s="4"/>
     </row>
     <row r="914" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K914" s="5"/>
+      <c r="K914" s="4"/>
     </row>
     <row r="915" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K915" s="5"/>
+      <c r="K915" s="4"/>
     </row>
     <row r="916" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K916" s="5"/>
+      <c r="K916" s="4"/>
     </row>
     <row r="917" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K917" s="5"/>
+      <c r="K917" s="4"/>
     </row>
     <row r="918" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K918" s="5"/>
+      <c r="K918" s="4"/>
     </row>
     <row r="919" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K919" s="5"/>
+      <c r="K919" s="4"/>
     </row>
     <row r="920" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K920" s="5"/>
+      <c r="K920" s="4"/>
     </row>
     <row r="921" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K921" s="5"/>
+      <c r="K921" s="4"/>
     </row>
     <row r="922" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K922" s="5"/>
+      <c r="K922" s="4"/>
     </row>
     <row r="923" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K923" s="5"/>
+      <c r="K923" s="4"/>
     </row>
     <row r="924" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K924" s="5"/>
+      <c r="K924" s="4"/>
     </row>
     <row r="925" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K925" s="5"/>
+      <c r="K925" s="4"/>
     </row>
     <row r="926" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K926" s="5"/>
+      <c r="K926" s="4"/>
     </row>
     <row r="927" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K927" s="5"/>
+      <c r="K927" s="4"/>
     </row>
     <row r="928" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K928" s="5"/>
+      <c r="K928" s="4"/>
     </row>
     <row r="929" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K929" s="5"/>
+      <c r="K929" s="4"/>
     </row>
     <row r="930" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K930" s="5"/>
+      <c r="K930" s="4"/>
     </row>
     <row r="931" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K931" s="5"/>
+      <c r="K931" s="4"/>
     </row>
     <row r="932" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K932" s="5"/>
+      <c r="K932" s="4"/>
     </row>
     <row r="933" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K933" s="5"/>
+      <c r="K933" s="4"/>
     </row>
     <row r="934" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K934" s="5"/>
+      <c r="K934" s="4"/>
     </row>
     <row r="935" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K935" s="5"/>
+      <c r="K935" s="4"/>
     </row>
     <row r="936" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K936" s="5"/>
+      <c r="K936" s="4"/>
     </row>
     <row r="937" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K937" s="5"/>
+      <c r="K937" s="4"/>
     </row>
     <row r="938" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K938" s="5"/>
+      <c r="K938" s="4"/>
     </row>
     <row r="939" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K939" s="5"/>
+      <c r="K939" s="4"/>
     </row>
     <row r="940" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K940" s="5"/>
+      <c r="K940" s="4"/>
     </row>
     <row r="941" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K941" s="5"/>
+      <c r="K941" s="4"/>
     </row>
     <row r="942" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K942" s="5"/>
+      <c r="K942" s="4"/>
     </row>
     <row r="943" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K943" s="5"/>
+      <c r="K943" s="4"/>
     </row>
     <row r="944" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K944" s="5"/>
+      <c r="K944" s="4"/>
     </row>
     <row r="945" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K945" s="5"/>
+      <c r="K945" s="4"/>
     </row>
     <row r="946" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K946" s="5"/>
+      <c r="K946" s="4"/>
     </row>
     <row r="947" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K947" s="5"/>
+      <c r="K947" s="4"/>
     </row>
     <row r="948" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K948" s="5"/>
+      <c r="K948" s="4"/>
     </row>
     <row r="949" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K949" s="5"/>
+      <c r="K949" s="4"/>
     </row>
     <row r="950" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K950" s="5"/>
+      <c r="K950" s="4"/>
     </row>
     <row r="951" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K951" s="5"/>
+      <c r="K951" s="4"/>
     </row>
     <row r="952" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K952" s="5"/>
+      <c r="K952" s="4"/>
     </row>
     <row r="953" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K953" s="5"/>
+      <c r="K953" s="4"/>
     </row>
     <row r="954" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K954" s="5"/>
+      <c r="K954" s="4"/>
     </row>
     <row r="955" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K955" s="5"/>
+      <c r="K955" s="4"/>
     </row>
     <row r="956" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K956" s="5"/>
+      <c r="K956" s="4"/>
     </row>
     <row r="957" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K957" s="5"/>
+      <c r="K957" s="4"/>
     </row>
     <row r="958" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K958" s="5"/>
+      <c r="K958" s="4"/>
     </row>
     <row r="959" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K959" s="5"/>
+      <c r="K959" s="4"/>
     </row>
     <row r="960" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K960" s="5"/>
+      <c r="K960" s="4"/>
     </row>
     <row r="961" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K961" s="5"/>
+      <c r="K961" s="4"/>
     </row>
     <row r="962" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K962" s="5"/>
+      <c r="K962" s="4"/>
     </row>
     <row r="963" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K963" s="5"/>
+      <c r="K963" s="4"/>
     </row>
     <row r="964" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K964" s="5"/>
+      <c r="K964" s="4"/>
     </row>
     <row r="965" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K965" s="5"/>
+      <c r="K965" s="4"/>
     </row>
     <row r="966" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K966" s="5"/>
+      <c r="K966" s="4"/>
     </row>
     <row r="967" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K967" s="5"/>
+      <c r="K967" s="4"/>
     </row>
     <row r="968" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K968" s="5"/>
+      <c r="K968" s="4"/>
     </row>
     <row r="969" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K969" s="5"/>
+      <c r="K969" s="4"/>
     </row>
     <row r="970" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K970" s="5"/>
+      <c r="K970" s="4"/>
     </row>
     <row r="971" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K971" s="5"/>
+      <c r="K971" s="4"/>
     </row>
     <row r="972" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K972" s="5"/>
+      <c r="K972" s="4"/>
     </row>
     <row r="973" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K973" s="5"/>
+      <c r="K973" s="4"/>
     </row>
     <row r="974" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K974" s="5"/>
+      <c r="K974" s="4"/>
     </row>
     <row r="975" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K975" s="5"/>
+      <c r="K975" s="4"/>
     </row>
     <row r="976" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K976" s="5"/>
+      <c r="K976" s="4"/>
     </row>
     <row r="977" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K977" s="5"/>
+      <c r="K977" s="4"/>
     </row>
     <row r="978" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K978" s="5"/>
+      <c r="K978" s="4"/>
     </row>
     <row r="979" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K979" s="5"/>
+      <c r="K979" s="4"/>
     </row>
     <row r="980" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K980" s="5"/>
+      <c r="K980" s="4"/>
     </row>
     <row r="981" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K981" s="5"/>
+      <c r="K981" s="4"/>
     </row>
     <row r="982" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K982" s="5"/>
+      <c r="K982" s="4"/>
     </row>
     <row r="983" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K983" s="5"/>
+      <c r="K983" s="4"/>
     </row>
     <row r="984" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K984" s="5"/>
+      <c r="K984" s="4"/>
     </row>
     <row r="985" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K985" s="5"/>
+      <c r="K985" s="4"/>
     </row>
     <row r="986" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K986" s="5"/>
+      <c r="K986" s="4"/>
     </row>
     <row r="987" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K987" s="5"/>
+      <c r="K987" s="4"/>
     </row>
     <row r="988" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K988" s="5"/>
+      <c r="K988" s="4"/>
     </row>
     <row r="989" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K989" s="5"/>
+      <c r="K989" s="4"/>
     </row>
     <row r="990" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K990" s="5"/>
+      <c r="K990" s="4"/>
     </row>
     <row r="991" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K991" s="5"/>
+      <c r="K991" s="4"/>
     </row>
     <row r="992" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K992" s="5"/>
+      <c r="K992" s="4"/>
     </row>
     <row r="993" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K993" s="5"/>
+      <c r="K993" s="4"/>
     </row>
     <row r="994" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K994" s="5"/>
+      <c r="K994" s="4"/>
     </row>
     <row r="995" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K995" s="5"/>
+      <c r="K995" s="4"/>
     </row>
     <row r="996" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K996" s="5"/>
+      <c r="K996" s="4"/>
     </row>
     <row r="997" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K997" s="5"/>
+      <c r="K997" s="4"/>
     </row>
     <row r="998" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K998" s="5"/>
+      <c r="K998" s="4"/>
     </row>
     <row r="999" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K999" s="5"/>
+      <c r="K999" s="4"/>
     </row>
     <row r="1000" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K1000" s="5"/>
+      <c r="K1000" s="4"/>
     </row>
     <row r="1001" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K1001" s="5"/>
+      <c r="K1001" s="4"/>
     </row>
     <row r="1002" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K1002" s="5"/>
+      <c r="K1002" s="4"/>
     </row>
     <row r="1003" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K1003" s="5"/>
+      <c r="K1003" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
